--- a/data/fluxo_de_caixa.xlsx
+++ b/data/fluxo_de_caixa.xlsx
@@ -539,13 +539,13 @@
         <v>2100.299999999814</v>
       </c>
       <c r="L2" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M2" t="n">
-        <v>12899.70000000019</v>
+        <v>147899.7000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>2987100.3</v>
+        <v>2852100.3</v>
       </c>
     </row>
     <row r="3">
@@ -574,13 +574,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2987100.3</v>
+        <v>2852100.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2091.268920029979</v>
+        <v>1996.755420030095</v>
       </c>
       <c r="K3" t="n">
-        <v>2091.268920029979</v>
+        <v>1996.755420030095</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2989191.56892003</v>
+        <v>2854097.05542003</v>
       </c>
     </row>
     <row r="4">
@@ -618,13 +618,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2989191.56892003</v>
+        <v>2854097.05542003</v>
       </c>
       <c r="J4" t="n">
-        <v>2092.733017400838</v>
+        <v>1998.153348499443</v>
       </c>
       <c r="K4" t="n">
-        <v>4184.001937430818</v>
+        <v>3994.908768529538</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2991284.301937431</v>
+        <v>2856095.208768529</v>
       </c>
     </row>
     <row r="5">
@@ -662,13 +662,13 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2991284.301937431</v>
+        <v>2856095.208768529</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4184.001937430818</v>
+        <v>3994.908768529538</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2991284.301937431</v>
+        <v>2856095.208768529</v>
       </c>
     </row>
     <row r="6">
@@ -706,13 +706,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2991284.301937431</v>
+        <v>2856095.208768529</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4184.001937430818</v>
+        <v>3994.908768529538</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2991284.301937431</v>
+        <v>2856095.208768529</v>
       </c>
     </row>
     <row r="7">
@@ -750,13 +750,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2991284.301937431</v>
+        <v>2856095.208768529</v>
       </c>
       <c r="J7" t="n">
-        <v>2094.198139786255</v>
+        <v>1999.552255658899</v>
       </c>
       <c r="K7" t="n">
-        <v>6278.200077217072</v>
+        <v>5994.461024188437</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -765,7 +765,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2993378.500077217</v>
+        <v>2858094.761024188</v>
       </c>
     </row>
     <row r="8">
@@ -794,13 +794,13 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2993378.500077217</v>
+        <v>2858094.761024188</v>
       </c>
       <c r="J8" t="n">
-        <v>2095.664287903812</v>
+        <v>2000.952142192982</v>
       </c>
       <c r="K8" t="n">
-        <v>8373.864365120884</v>
+        <v>7995.413166381419</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2995474.164365121</v>
+        <v>2860095.713166381</v>
       </c>
     </row>
     <row r="9">
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2995474.164365121</v>
+        <v>2860095.713166381</v>
       </c>
       <c r="J9" t="n">
-        <v>2097.131462472025</v>
+        <v>2002.353008787613</v>
       </c>
       <c r="K9" t="n">
-        <v>10470.99582759291</v>
+        <v>9997.766175169032</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2997571.295827593</v>
+        <v>2862098.066175169</v>
       </c>
     </row>
     <row r="10">
@@ -882,13 +882,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2997571.295827593</v>
+        <v>2862098.066175169</v>
       </c>
       <c r="J10" t="n">
-        <v>2098.599664208945</v>
+        <v>2003.754856129177</v>
       </c>
       <c r="K10" t="n">
-        <v>12569.59549180185</v>
+        <v>12001.52103129821</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2999669.895491802</v>
+        <v>2864101.821031298</v>
       </c>
     </row>
     <row r="11">
@@ -926,13 +926,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2999669.895491802</v>
+        <v>2864101.821031298</v>
       </c>
       <c r="J11" t="n">
-        <v>2100.068893833552</v>
+        <v>2005.157684904058</v>
       </c>
       <c r="K11" t="n">
-        <v>14669.66438563541</v>
+        <v>14006.67871620227</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3001769.964385635</v>
+        <v>2866106.978716202</v>
       </c>
     </row>
     <row r="12">
@@ -970,13 +970,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3001769.964385635</v>
+        <v>2866106.978716202</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>14669.66438563541</v>
+        <v>14006.67871620227</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3001769.964385635</v>
+        <v>2866106.978716202</v>
       </c>
     </row>
     <row r="13">
@@ -1018,13 +1018,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3001769.964385635</v>
+        <v>2866106.978716202</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>14669.66438563541</v>
+        <v>14006.67871620227</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3001769.964385635</v>
+        <v>2866106.978716202</v>
       </c>
     </row>
     <row r="14">
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3001769.964385635</v>
+        <v>2866106.978716202</v>
       </c>
       <c r="J14" t="n">
-        <v>2101.539152066223</v>
+        <v>2006.561495799106</v>
       </c>
       <c r="K14" t="n">
-        <v>16771.20353770163</v>
+        <v>16013.24021200137</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3003871.503537701</v>
+        <v>2868113.540212001</v>
       </c>
     </row>
     <row r="15">
@@ -1106,13 +1106,13 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3003871.503537701</v>
+        <v>2868113.540212001</v>
       </c>
       <c r="J15" t="n">
-        <v>2103.010439626873</v>
+        <v>2007.966289502569</v>
       </c>
       <c r="K15" t="n">
-        <v>18874.2139773285</v>
+        <v>18021.20650150394</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3005974.513977328</v>
+        <v>2870121.506501504</v>
       </c>
     </row>
     <row r="16">
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3005974.513977328</v>
+        <v>2870121.506501504</v>
       </c>
       <c r="J16" t="n">
-        <v>2104.482757235412</v>
+        <v>2009.372066701762</v>
       </c>
       <c r="K16" t="n">
-        <v>20978.69673456391</v>
+        <v>20030.5785682057</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3008078.996734564</v>
+        <v>2872130.878568206</v>
       </c>
     </row>
     <row r="17">
@@ -1194,13 +1194,13 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3008078.996734564</v>
+        <v>2872130.878568206</v>
       </c>
       <c r="J17" t="n">
-        <v>2105.956105613615</v>
+        <v>2010.7788280854</v>
       </c>
       <c r="K17" t="n">
-        <v>23084.65284017753</v>
+        <v>22041.3573962911</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3010184.952840177</v>
+        <v>2874141.657396291</v>
       </c>
     </row>
     <row r="18">
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3010184.952840177</v>
+        <v>2874141.657396291</v>
       </c>
       <c r="J18" t="n">
-        <v>2107.430485483259</v>
+        <v>2012.186574343126</v>
       </c>
       <c r="K18" t="n">
-        <v>25192.08332566079</v>
+        <v>24053.54397063423</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3012292.383325661</v>
+        <v>2876153.843970634</v>
       </c>
     </row>
     <row r="19">
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3012292.383325661</v>
+        <v>2876153.843970634</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>25192.08332566079</v>
+        <v>24053.54397063423</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3012292.383325661</v>
+        <v>2876153.843970634</v>
       </c>
     </row>
     <row r="20">
@@ -1326,13 +1326,13 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3012292.383325661</v>
+        <v>2876153.843970634</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>25192.08332566079</v>
+        <v>24053.54397063423</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3012292.383325661</v>
+        <v>2876153.843970634</v>
       </c>
     </row>
     <row r="21">
@@ -1370,13 +1370,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3012292.383325661</v>
+        <v>2876153.843970634</v>
       </c>
       <c r="J21" t="n">
-        <v>2108.905897566117</v>
+        <v>2013.595306163654</v>
       </c>
       <c r="K21" t="n">
-        <v>27300.9892232269</v>
+        <v>26067.13927679788</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3014401.289223227</v>
+        <v>2878167.439276798</v>
       </c>
     </row>
     <row r="22">
@@ -1414,13 +1414,13 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3014401.289223227</v>
+        <v>2878167.439276798</v>
       </c>
       <c r="J22" t="n">
-        <v>2110.382342584897</v>
+        <v>2015.005024237558</v>
       </c>
       <c r="K22" t="n">
-        <v>29411.3715658118</v>
+        <v>28082.14430103544</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3016511.671565812</v>
+        <v>2880182.444301035</v>
       </c>
     </row>
     <row r="23">
@@ -1458,13 +1458,13 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3016511.671565812</v>
+        <v>2880182.444301035</v>
       </c>
       <c r="J23" t="n">
-        <v>2111.859821263235</v>
+        <v>2016.41572925495</v>
       </c>
       <c r="K23" t="n">
-        <v>31523.23138707504</v>
+        <v>30098.56003029039</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3018623.531387075</v>
+        <v>2882198.86003029</v>
       </c>
     </row>
     <row r="24">
@@ -1502,13 +1502,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3018623.531387075</v>
+        <v>2882198.86003029</v>
       </c>
       <c r="J24" t="n">
-        <v>2113.338334323838</v>
+        <v>2017.827421907336</v>
       </c>
       <c r="K24" t="n">
-        <v>33636.56972139888</v>
+        <v>32116.38745219773</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1517,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3020736.869721399</v>
+        <v>2884216.687452198</v>
       </c>
     </row>
     <row r="25">
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3020736.869721399</v>
+        <v>2884216.687452198</v>
       </c>
       <c r="J25" t="n">
-        <v>2114.817882491741</v>
+        <v>2019.240102885291</v>
       </c>
       <c r="K25" t="n">
-        <v>35751.38760389062</v>
+        <v>34135.62755508302</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3022851.68760389</v>
+        <v>2886235.927555083</v>
       </c>
     </row>
     <row r="26">
@@ -1590,13 +1590,13 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3022851.68760389</v>
+        <v>2886235.927555083</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>35751.38760389062</v>
+        <v>34135.62755508302</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3022851.68760389</v>
+        <v>2886235.927555083</v>
       </c>
     </row>
     <row r="27">
@@ -1634,13 +1634,13 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3022851.68760389</v>
+        <v>2886235.927555083</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>35751.38760389062</v>
+        <v>34135.62755508302</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3022851.68760389</v>
+        <v>2886235.927555083</v>
       </c>
     </row>
     <row r="28">
@@ -1678,13 +1678,13 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3022851.68760389</v>
+        <v>2886235.927555083</v>
       </c>
       <c r="J28" t="n">
-        <v>2116.298466491513</v>
+        <v>2020.653772881255</v>
       </c>
       <c r="K28" t="n">
-        <v>37867.68607038213</v>
+        <v>36156.28132796427</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3024967.986070382</v>
+        <v>2888256.581327964</v>
       </c>
     </row>
     <row r="29">
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3024967.986070382</v>
+        <v>2888256.581327964</v>
       </c>
       <c r="J29" t="n">
-        <v>2117.780087047722</v>
+        <v>2022.068432587665</v>
       </c>
       <c r="K29" t="n">
-        <v>39985.46615742985</v>
+        <v>38178.34976055194</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3027085.76615743</v>
+        <v>2890278.649760552</v>
       </c>
     </row>
     <row r="30">
@@ -1766,13 +1766,13 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>3027085.76615743</v>
+        <v>2890278.649760552</v>
       </c>
       <c r="J30" t="n">
-        <v>2119.262744886801</v>
+        <v>2023.484082697425</v>
       </c>
       <c r="K30" t="n">
-        <v>42104.72890231665</v>
+        <v>40201.83384324936</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3029205.028902316</v>
+        <v>2892302.133843249</v>
       </c>
     </row>
     <row r="31">
@@ -1810,13 +1810,13 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3029205.028902316</v>
+        <v>2892302.133843249</v>
       </c>
       <c r="J31" t="n">
-        <v>2120.746440734249</v>
+        <v>2024.90072390344</v>
       </c>
       <c r="K31" t="n">
-        <v>44225.4753430509</v>
+        <v>42226.7345671528</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3031325.775343051</v>
+        <v>2894327.034567153</v>
       </c>
     </row>
     <row r="32">
@@ -1854,13 +1854,13 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3031325.775343051</v>
+        <v>2894327.034567153</v>
       </c>
       <c r="J32" t="n">
-        <v>2122.231175317429</v>
+        <v>2026.318356900476</v>
       </c>
       <c r="K32" t="n">
-        <v>46347.70651836833</v>
+        <v>44253.05292405328</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1869,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3033448.006518368</v>
+        <v>2896353.352924053</v>
       </c>
     </row>
     <row r="33">
@@ -1898,13 +1898,13 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3033448.006518368</v>
+        <v>2896353.352924053</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>46347.70651836833</v>
+        <v>44253.05292405328</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3033448.006518368</v>
+        <v>2896353.352924053</v>
       </c>
     </row>
     <row r="34">
@@ -1946,13 +1946,13 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3033448.006518368</v>
+        <v>2896353.352924053</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>46347.70651836833</v>
+        <v>44253.05292405328</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3033448.006518368</v>
+        <v>2896353.352924053</v>
       </c>
     </row>
     <row r="35">
@@ -1990,22 +1990,22 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>3033448.006518368</v>
+        <v>2896353.352924053</v>
       </c>
       <c r="J35" t="n">
-        <v>2123.716949363239</v>
+        <v>2027.736982381903</v>
       </c>
       <c r="K35" t="n">
-        <v>48471.42346773157</v>
+        <v>46280.78990643518</v>
       </c>
       <c r="L35" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M35" t="n">
-        <v>-33471.42346773157</v>
+        <v>103719.2100935648</v>
       </c>
       <c r="N35" t="n">
-        <v>3020571.723467731</v>
+        <v>2748381.089906435</v>
       </c>
     </row>
     <row r="36">
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>3020571.723467731</v>
+        <v>2748381.089906435</v>
       </c>
       <c r="J36" t="n">
-        <v>2114.702263599727</v>
+        <v>1924.141601043288</v>
       </c>
       <c r="K36" t="n">
-        <v>2114.702263599727</v>
+        <v>1924.141601043288</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3022686.425731331</v>
+        <v>2750305.231507478</v>
       </c>
     </row>
     <row r="37">
@@ -2078,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3022686.425731331</v>
+        <v>2750305.231507478</v>
       </c>
       <c r="J37" t="n">
-        <v>2116.182766654529</v>
+        <v>1925.488692578394</v>
       </c>
       <c r="K37" t="n">
-        <v>4230.885030254256</v>
+        <v>3849.630293621682</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3024802.608497986</v>
+        <v>2752230.720200057</v>
       </c>
     </row>
     <row r="38">
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>3024802.608497986</v>
+        <v>2752230.720200057</v>
       </c>
       <c r="J38" t="n">
-        <v>2117.664306209423</v>
+        <v>1926.836727212183</v>
       </c>
       <c r="K38" t="n">
-        <v>6348.549336463679</v>
+        <v>5776.467020833865</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3026920.272804195</v>
+        <v>2754157.556927269</v>
       </c>
     </row>
     <row r="39">
@@ -2166,13 +2166,13 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3026920.272804195</v>
+        <v>2754157.556927269</v>
       </c>
       <c r="J39" t="n">
-        <v>2119.146882990375</v>
+        <v>1928.185705604497</v>
       </c>
       <c r="K39" t="n">
-        <v>8467.696219454054</v>
+        <v>7704.652726438362</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3029039.419687185</v>
+        <v>2756085.742632873</v>
       </c>
     </row>
     <row r="40">
@@ -2210,13 +2210,13 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3029039.419687185</v>
+        <v>2756085.742632873</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>8467.696219454054</v>
+        <v>7704.652726438362</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3029039.419687185</v>
+        <v>2756085.742632873</v>
       </c>
     </row>
     <row r="41">
@@ -2254,13 +2254,13 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>3029039.419687185</v>
+        <v>2756085.742632873</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>8467.696219454054</v>
+        <v>7704.652726438362</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3029039.419687185</v>
+        <v>2756085.742632873</v>
       </c>
     </row>
     <row r="42">
@@ -2298,13 +2298,13 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>3029039.419687185</v>
+        <v>2756085.742632873</v>
       </c>
       <c r="J42" t="n">
-        <v>2120.630497722887</v>
+        <v>1929.535628417041</v>
       </c>
       <c r="K42" t="n">
-        <v>10588.32671717694</v>
+        <v>9634.188354855403</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3031160.050184908</v>
+        <v>2758015.27826129</v>
       </c>
     </row>
     <row r="43">
@@ -2342,13 +2342,13 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3031160.050184908</v>
+        <v>2758015.27826129</v>
       </c>
       <c r="J43" t="n">
-        <v>2122.11515113432</v>
+        <v>1930.886496310588</v>
       </c>
       <c r="K43" t="n">
-        <v>12710.44186831126</v>
+        <v>11565.07485116599</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2357,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3033282.165336043</v>
+        <v>2759946.164757601</v>
       </c>
     </row>
     <row r="44">
@@ -2386,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3033282.165336043</v>
+        <v>2759946.164757601</v>
       </c>
       <c r="J44" t="n">
-        <v>2123.600843951572</v>
+        <v>1932.238309946842</v>
       </c>
       <c r="K44" t="n">
-        <v>14834.04271226283</v>
+        <v>13497.31316111283</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3035405.766179994</v>
+        <v>2761878.403067548</v>
       </c>
     </row>
     <row r="45">
@@ -2430,13 +2430,13 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3035405.766179994</v>
+        <v>2761878.403067548</v>
       </c>
       <c r="J45" t="n">
-        <v>2125.087576902471</v>
+        <v>1933.591069987509</v>
       </c>
       <c r="K45" t="n">
-        <v>16959.1302891653</v>
+        <v>15430.90423110034</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3037530.853756897</v>
+        <v>2763811.994137535</v>
       </c>
     </row>
     <row r="46">
@@ -2474,13 +2474,13 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>3037530.853756897</v>
+        <v>2763811.994137535</v>
       </c>
       <c r="J46" t="n">
-        <v>2126.575350715313</v>
+        <v>1934.94477709569</v>
       </c>
       <c r="K46" t="n">
-        <v>19085.70563988062</v>
+        <v>17365.84900819603</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3039657.429107612</v>
+        <v>2765746.938914631</v>
       </c>
     </row>
     <row r="47">
@@ -2522,13 +2522,13 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>3039657.429107612</v>
+        <v>2765746.938914631</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>19085.70563988062</v>
+        <v>17365.84900819603</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3039657.429107612</v>
+        <v>2765746.938914631</v>
       </c>
     </row>
     <row r="48">
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>3039657.429107612</v>
+        <v>2765746.938914631</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>19085.70563988062</v>
+        <v>17365.84900819603</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3039657.429107612</v>
+        <v>2765746.938914631</v>
       </c>
     </row>
     <row r="49">
@@ -2610,13 +2610,13 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>3039657.429107612</v>
+        <v>2765746.938914631</v>
       </c>
       <c r="J49" t="n">
-        <v>2128.064166118391</v>
+        <v>1936.299431934021</v>
       </c>
       <c r="K49" t="n">
-        <v>21213.76980599901</v>
+        <v>19302.14844013005</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2625,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3041785.49327373</v>
+        <v>2767683.238346565</v>
       </c>
     </row>
     <row r="50">
@@ -2654,13 +2654,13 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>3041785.49327373</v>
+        <v>2767683.238346565</v>
       </c>
       <c r="J50" t="n">
-        <v>2129.55402384093</v>
+        <v>1937.655035166536</v>
       </c>
       <c r="K50" t="n">
-        <v>23343.32382983994</v>
+        <v>21239.80347529659</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3043915.047297571</v>
+        <v>2769620.893381732</v>
       </c>
     </row>
     <row r="51">
@@ -2698,13 +2698,13 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>3043915.047297571</v>
+        <v>2769620.893381732</v>
       </c>
       <c r="J51" t="n">
-        <v>2131.044924613088</v>
+        <v>1939.011587456334</v>
       </c>
       <c r="K51" t="n">
-        <v>25474.36875445303</v>
+        <v>23178.81506275292</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3046046.092222184</v>
+        <v>2771559.904969188</v>
       </c>
     </row>
     <row r="52">
@@ -2746,13 +2746,13 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>3046046.092222184</v>
+        <v>2771559.904969188</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>25474.36875445303</v>
+        <v>23178.81506275292</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3046046.092222184</v>
+        <v>2771559.904969188</v>
       </c>
     </row>
     <row r="53">
@@ -2790,13 +2790,13 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>3046046.092222184</v>
+        <v>2771559.904969188</v>
       </c>
       <c r="J53" t="n">
-        <v>2132.536869164556</v>
+        <v>1940.369089468848</v>
       </c>
       <c r="K53" t="n">
-        <v>27606.90562361758</v>
+        <v>25119.18415222177</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3048178.629091349</v>
+        <v>2773500.274058657</v>
       </c>
     </row>
     <row r="54">
@@ -2834,13 +2834,13 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>3048178.629091349</v>
+        <v>2773500.274058657</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>27606.90562361758</v>
+        <v>25119.18415222177</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3048178.629091349</v>
+        <v>2773500.274058657</v>
       </c>
     </row>
     <row r="55">
@@ -2878,13 +2878,13 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>3048178.629091349</v>
+        <v>2773500.274058657</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>27606.90562361758</v>
+        <v>25119.18415222177</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3048178.629091349</v>
+        <v>2773500.274058657</v>
       </c>
     </row>
     <row r="56">
@@ -2922,13 +2922,13 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>3048178.629091349</v>
+        <v>2773500.274058657</v>
       </c>
       <c r="J56" t="n">
-        <v>2134.029858226888</v>
+        <v>1941.727541868575</v>
       </c>
       <c r="K56" t="n">
-        <v>29740.93548184447</v>
+        <v>27060.91169409035</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3050312.658949576</v>
+        <v>2775442.001600525</v>
       </c>
     </row>
     <row r="57">
@@ -2966,13 +2966,13 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>3050312.658949576</v>
+        <v>2775442.001600525</v>
       </c>
       <c r="J57" t="n">
-        <v>2135.523892530706</v>
+        <v>1943.08694532048</v>
       </c>
       <c r="K57" t="n">
-        <v>31876.45937437518</v>
+        <v>29003.99863941083</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3052448.182842107</v>
+        <v>2777385.088545846</v>
       </c>
     </row>
     <row r="58">
@@ -3010,13 +3010,13 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>3052448.182842107</v>
+        <v>2777385.088545846</v>
       </c>
       <c r="J58" t="n">
-        <v>2137.018972807564</v>
+        <v>1944.447300490923</v>
       </c>
       <c r="K58" t="n">
-        <v>34013.47834718274</v>
+        <v>30948.44593990175</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3054585.201814914</v>
+        <v>2779329.535846337</v>
       </c>
     </row>
     <row r="59">
@@ -3054,13 +3054,13 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>3054585.201814914</v>
+        <v>2779329.535846337</v>
       </c>
       <c r="J59" t="n">
-        <v>2138.515099790413</v>
+        <v>1945.808608045802</v>
       </c>
       <c r="K59" t="n">
-        <v>36151.99344697315</v>
+        <v>32894.25454794755</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3056723.716914705</v>
+        <v>2781275.344454383</v>
       </c>
     </row>
     <row r="60">
@@ -3098,13 +3098,13 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>3056723.716914705</v>
+        <v>2781275.344454383</v>
       </c>
       <c r="J60" t="n">
-        <v>2140.012274211738</v>
+        <v>1947.170868652407</v>
       </c>
       <c r="K60" t="n">
-        <v>38292.00572118489</v>
+        <v>34841.42541659996</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3058863.729188916</v>
+        <v>2783222.515323035</v>
       </c>
     </row>
     <row r="61">
@@ -3142,13 +3142,13 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>3058863.729188916</v>
+        <v>2783222.515323035</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>38292.00572118489</v>
+        <v>34841.42541659996</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3058863.729188916</v>
+        <v>2783222.515323035</v>
       </c>
     </row>
     <row r="62">
@@ -3190,13 +3190,13 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>3058863.729188916</v>
+        <v>2783222.515323035</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>38292.00572118489</v>
+        <v>34841.42541659996</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3058863.729188916</v>
+        <v>2783222.515323035</v>
       </c>
     </row>
     <row r="63">
@@ -3234,22 +3234,22 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>3058863.729188916</v>
+        <v>2783222.515323035</v>
       </c>
       <c r="J63" t="n">
-        <v>2141.510496804956</v>
+        <v>1948.534082977567</v>
       </c>
       <c r="K63" t="n">
-        <v>40433.51621798985</v>
+        <v>36789.95949957753</v>
       </c>
       <c r="L63" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M63" t="n">
-        <v>-25433.51621798985</v>
+        <v>113210.0405004225</v>
       </c>
       <c r="N63" t="n">
-        <v>3046005.239685721</v>
+        <v>2635171.049406013</v>
       </c>
     </row>
     <row r="64">
@@ -3278,13 +3278,13 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>3046005.239685721</v>
+        <v>2635171.049406013</v>
       </c>
       <c r="J64" t="n">
-        <v>2132.508268303704</v>
+        <v>1844.883251688909</v>
       </c>
       <c r="K64" t="n">
-        <v>2132.508268303704</v>
+        <v>1844.883251688909</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3048137.747954025</v>
+        <v>2637015.932657701</v>
       </c>
     </row>
     <row r="65">
@@ -3322,13 +3322,13 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>3048137.747954025</v>
+        <v>2637015.932657701</v>
       </c>
       <c r="J65" t="n">
-        <v>2134.0012373426</v>
+        <v>1846.174854453653</v>
       </c>
       <c r="K65" t="n">
-        <v>4266.509505646303</v>
+        <v>3691.058106142562</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3337,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3050271.749191368</v>
+        <v>2638862.107512155</v>
       </c>
     </row>
     <row r="66">
@@ -3366,13 +3366,13 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>3050271.749191368</v>
+        <v>2638862.107512155</v>
       </c>
       <c r="J66" t="n">
-        <v>2135.495251609012</v>
+        <v>1847.467361469287</v>
       </c>
       <c r="K66" t="n">
-        <v>6402.004757255316</v>
+        <v>5538.525467611849</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3052407.244442977</v>
+        <v>2640709.574873624</v>
       </c>
     </row>
     <row r="67">
@@ -3410,13 +3410,13 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>3052407.244442977</v>
+        <v>2640709.574873624</v>
       </c>
       <c r="J67" t="n">
-        <v>2136.990311834496</v>
+        <v>1848.760773369111</v>
       </c>
       <c r="K67" t="n">
-        <v>8538.995069089811</v>
+        <v>7387.28624098096</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3054544.234754811</v>
+        <v>2642558.335646993</v>
       </c>
     </row>
     <row r="68">
@@ -3454,13 +3454,13 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>3054544.234754811</v>
+        <v>2642558.335646993</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>8538.995069089811</v>
+        <v>7387.28624098096</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3054544.234754811</v>
+        <v>2642558.335646993</v>
       </c>
     </row>
     <row r="69">
@@ -3498,13 +3498,13 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>3054544.234754811</v>
+        <v>2642558.335646993</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>8538.995069089811</v>
+        <v>7387.28624098096</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3054544.234754811</v>
+        <v>2642558.335646993</v>
       </c>
     </row>
     <row r="70">
@@ -3542,13 +3542,13 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>3054544.234754811</v>
+        <v>2642558.335646993</v>
       </c>
       <c r="J70" t="n">
-        <v>2138.486418752</v>
+        <v>1850.055090786424</v>
       </c>
       <c r="K70" t="n">
-        <v>10677.48148784181</v>
+        <v>9237.341331767384</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3557,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3056682.721173563</v>
+        <v>2644408.39073778</v>
       </c>
     </row>
     <row r="71">
@@ -3586,13 +3586,13 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>3056682.721173563</v>
+        <v>2644408.39073778</v>
       </c>
       <c r="J71" t="n">
-        <v>2139.983573093545</v>
+        <v>1851.350314355455</v>
       </c>
       <c r="K71" t="n">
-        <v>12817.46506093536</v>
+        <v>11088.69164612284</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3601,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3058822.704746657</v>
+        <v>2646259.741052135</v>
       </c>
     </row>
     <row r="72">
@@ -3630,13 +3630,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>3058822.704746657</v>
+        <v>2646259.741052135</v>
       </c>
       <c r="J72" t="n">
-        <v>2141.481775593013</v>
+        <v>1852.646444710437</v>
       </c>
       <c r="K72" t="n">
-        <v>14958.94683652837</v>
+        <v>12941.33809083328</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3060964.18652225</v>
+        <v>2648112.387496846</v>
       </c>
     </row>
     <row r="73">
@@ -3674,13 +3674,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>3060964.18652225</v>
+        <v>2648112.387496846</v>
       </c>
       <c r="J73" t="n">
-        <v>2142.981026984286</v>
+        <v>1853.943482486531</v>
       </c>
       <c r="K73" t="n">
-        <v>17101.92786351265</v>
+        <v>14795.28157331981</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3063107.167549234</v>
+        <v>2649966.330979332</v>
       </c>
     </row>
     <row r="74">
@@ -3718,13 +3718,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>3063107.167549234</v>
+        <v>2649966.330979332</v>
       </c>
       <c r="J74" t="n">
-        <v>2144.481328001246</v>
+        <v>1855.241428318433</v>
       </c>
       <c r="K74" t="n">
-        <v>19246.4091915139</v>
+        <v>16650.52300163824</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3065251.648877235</v>
+        <v>2651821.572407651</v>
       </c>
     </row>
     <row r="75">
@@ -3762,13 +3762,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>3065251.648877235</v>
+        <v>2651821.572407651</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>19246.4091915139</v>
+        <v>16650.52300163824</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3065251.648877235</v>
+        <v>2651821.572407651</v>
       </c>
     </row>
     <row r="76">
@@ -3806,13 +3806,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>3065251.648877235</v>
+        <v>2651821.572407651</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>19246.4091915139</v>
+        <v>16650.52300163824</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3065251.648877235</v>
+        <v>2651821.572407651</v>
       </c>
     </row>
     <row r="77">
@@ -3850,13 +3850,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>3065251.648877235</v>
+        <v>2651821.572407651</v>
       </c>
       <c r="J77" t="n">
-        <v>2145.982679378707</v>
+        <v>1856.540282842703</v>
       </c>
       <c r="K77" t="n">
-        <v>21392.39187089261</v>
+        <v>18507.06328448094</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3067397.631556614</v>
+        <v>2653678.112690493</v>
       </c>
     </row>
     <row r="78">
@@ -3894,13 +3894,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>3067397.631556614</v>
+        <v>2653678.112690493</v>
       </c>
       <c r="J78" t="n">
-        <v>2147.485081852879</v>
+        <v>1857.840046694502</v>
       </c>
       <c r="K78" t="n">
-        <v>23539.87695274549</v>
+        <v>20364.90333117545</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3069545.116638467</v>
+        <v>2655535.952737188</v>
       </c>
     </row>
     <row r="79">
@@ -3938,13 +3938,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>3069545.116638467</v>
+        <v>2655535.952737188</v>
       </c>
       <c r="J79" t="n">
-        <v>2148.988536158577</v>
+        <v>1859.140720511321</v>
       </c>
       <c r="K79" t="n">
-        <v>25688.86548890406</v>
+        <v>22224.04405168677</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3071694.105174625</v>
+        <v>2657395.093457699</v>
       </c>
     </row>
     <row r="80">
@@ -3982,13 +3982,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>3071694.105174625</v>
+        <v>2657395.093457699</v>
       </c>
       <c r="J80" t="n">
-        <v>2150.493043032475</v>
+        <v>1860.442304929718</v>
       </c>
       <c r="K80" t="n">
-        <v>27839.35853193654</v>
+        <v>24084.48635661649</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3073844.598217658</v>
+        <v>2659255.535762629</v>
       </c>
     </row>
     <row r="81">
@@ -4026,13 +4026,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>3073844.598217658</v>
+        <v>2659255.535762629</v>
       </c>
       <c r="J81" t="n">
-        <v>2151.998603212181</v>
+        <v>1861.744800587185</v>
       </c>
       <c r="K81" t="n">
-        <v>29991.35713514872</v>
+        <v>25946.23115720367</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3075996.59682087</v>
+        <v>2661117.280563216</v>
       </c>
     </row>
     <row r="82">
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>3075996.59682087</v>
+        <v>2661117.280563216</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>29991.35713514872</v>
+        <v>25946.23115720367</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3075996.59682087</v>
+        <v>2661117.280563216</v>
       </c>
     </row>
     <row r="83">
@@ -4114,13 +4114,13 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>3075996.59682087</v>
+        <v>2661117.280563216</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>29991.35713514872</v>
+        <v>25946.23115720367</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3075996.59682087</v>
+        <v>2661117.280563216</v>
       </c>
     </row>
     <row r="84">
@@ -4158,13 +4158,13 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>3075996.59682087</v>
+        <v>2661117.280563216</v>
       </c>
       <c r="J84" t="n">
-        <v>2153.505217434373</v>
+        <v>1863.048208122142</v>
       </c>
       <c r="K84" t="n">
-        <v>32144.86235258309</v>
+        <v>27809.27936532581</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3078150.102038304</v>
+        <v>2662980.328771338</v>
       </c>
     </row>
     <row r="85">
@@ -4202,13 +4202,13 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>3078150.102038304</v>
+        <v>2662980.328771338</v>
       </c>
       <c r="J85" t="n">
-        <v>2155.012886437122</v>
+        <v>1864.352528172545</v>
       </c>
       <c r="K85" t="n">
-        <v>34299.87523902021</v>
+        <v>29673.63189349836</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4217,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3080305.114924741</v>
+        <v>2664844.681299511</v>
       </c>
     </row>
     <row r="86">
@@ -4246,13 +4246,13 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>3080305.114924741</v>
+        <v>2664844.681299511</v>
       </c>
       <c r="J86" t="n">
-        <v>2156.521610958967</v>
+        <v>1865.657761377748</v>
       </c>
       <c r="K86" t="n">
-        <v>36456.39684997918</v>
+        <v>31539.28965487611</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4261,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3082461.6365357</v>
+        <v>2666710.339060889</v>
       </c>
     </row>
     <row r="87">
@@ -4294,13 +4294,13 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>3082461.6365357</v>
+        <v>2666710.339060889</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>36456.39684997918</v>
+        <v>31539.28965487611</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4309,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3082461.6365357</v>
+        <v>2666710.339060889</v>
       </c>
     </row>
     <row r="88">
@@ -4338,13 +4338,13 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>3082461.6365357</v>
+        <v>2666710.339060889</v>
       </c>
       <c r="J88" t="n">
-        <v>2158.031391738448</v>
+        <v>1866.963908376638</v>
       </c>
       <c r="K88" t="n">
-        <v>38614.42824171763</v>
+        <v>33406.25356325274</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4353,7 +4353,7 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3084619.667927439</v>
+        <v>2668577.302969265</v>
       </c>
     </row>
     <row r="89">
@@ -4382,13 +4382,13 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>3084619.667927439</v>
+        <v>2668577.302969265</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>38614.42824171763</v>
+        <v>33406.25356325274</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4397,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3084619.667927439</v>
+        <v>2668577.302969265</v>
       </c>
     </row>
     <row r="90">
@@ -4426,13 +4426,13 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>3084619.667927439</v>
+        <v>2668577.302969265</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>38614.42824171763</v>
+        <v>33406.25356325274</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3084619.667927439</v>
+        <v>2668577.302969265</v>
       </c>
     </row>
     <row r="91">
@@ -4470,13 +4470,13 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>3084619.667927439</v>
+        <v>2668577.302969265</v>
       </c>
       <c r="J91" t="n">
-        <v>2159.542229515966</v>
+        <v>1868.270969808567</v>
       </c>
       <c r="K91" t="n">
-        <v>40773.9704712336</v>
+        <v>35274.52453306131</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3086779.210156955</v>
+        <v>2670445.573939074</v>
       </c>
     </row>
     <row r="92">
@@ -4514,13 +4514,13 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>3086779.210156955</v>
+        <v>2670445.573939074</v>
       </c>
       <c r="J92" t="n">
-        <v>2161.054125030991</v>
+        <v>1869.578946314752</v>
       </c>
       <c r="K92" t="n">
-        <v>42935.02459626459</v>
+        <v>37144.10347937606</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3088940.264281986</v>
+        <v>2672315.152885389</v>
       </c>
     </row>
     <row r="93">
@@ -4558,13 +4558,13 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>3088940.264281986</v>
+        <v>2672315.152885389</v>
       </c>
       <c r="J93" t="n">
-        <v>2162.567079023924</v>
+        <v>1870.887838535011</v>
       </c>
       <c r="K93" t="n">
-        <v>45097.59167528851</v>
+        <v>39014.99131791107</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3091102.83136101</v>
+        <v>2674186.040723924</v>
       </c>
     </row>
     <row r="94">
@@ -4606,13 +4606,13 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>3091102.83136101</v>
+        <v>2674186.040723924</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>45097.59167528851</v>
+        <v>39014.99131791107</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3091102.83136101</v>
+        <v>2674186.040723924</v>
       </c>
     </row>
     <row r="95">
@@ -4650,22 +4650,22 @@
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>3091102.83136101</v>
+        <v>2674186.040723924</v>
       </c>
       <c r="J95" t="n">
-        <v>2164.081092235632</v>
+        <v>1872.197647110559</v>
       </c>
       <c r="K95" t="n">
-        <v>47261.67276752414</v>
+        <v>40887.18896502163</v>
       </c>
       <c r="L95" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M95" t="n">
-        <v>-32261.67276752414</v>
+        <v>109112.8110349784</v>
       </c>
       <c r="N95" t="n">
-        <v>3078266.912453245</v>
+        <v>2526058.238371034</v>
       </c>
     </row>
     <row r="96">
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>3078266.912453245</v>
+        <v>2526058.238371034</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3078266.912453245</v>
+        <v>2526058.238371034</v>
       </c>
     </row>
     <row r="97">
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>3078266.912453245</v>
+        <v>2526058.238371034</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3078266.912453245</v>
+        <v>2526058.238371034</v>
       </c>
     </row>
     <row r="98">
@@ -4782,13 +4782,13 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>3078266.912453245</v>
+        <v>2526058.238371034</v>
       </c>
       <c r="J98" t="n">
-        <v>2155.0946654086</v>
+        <v>1768.493372683413</v>
       </c>
       <c r="K98" t="n">
-        <v>2155.0946654086</v>
+        <v>1768.493372683413</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3080422.007118654</v>
+        <v>2527826.731743718</v>
       </c>
     </row>
     <row r="99">
@@ -4826,13 +4826,13 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>3080422.007118654</v>
+        <v>2527826.731743718</v>
       </c>
       <c r="J99" t="n">
-        <v>2156.603447183501</v>
+        <v>1769.731494893786</v>
       </c>
       <c r="K99" t="n">
-        <v>4311.698112592101</v>
+        <v>3538.224867577199</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3082578.610565837</v>
+        <v>2529596.463238611</v>
       </c>
     </row>
     <row r="100">
@@ -4870,13 +4870,13 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>3082578.610565837</v>
+        <v>2529596.463238611</v>
       </c>
       <c r="J100" t="n">
-        <v>2158.113285257015</v>
+        <v>1770.970483913086</v>
       </c>
       <c r="K100" t="n">
-        <v>6469.811397849116</v>
+        <v>5309.195351490285</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3084736.723851094</v>
+        <v>2531367.433722524</v>
       </c>
     </row>
     <row r="101">
@@ -4914,13 +4914,13 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>3084736.723851094</v>
+        <v>2531367.433722524</v>
       </c>
       <c r="J101" t="n">
-        <v>2159.624180368148</v>
+        <v>1772.210340349004</v>
       </c>
       <c r="K101" t="n">
-        <v>8629.435578217264</v>
+        <v>7081.405691839289</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -4929,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3086896.348031463</v>
+        <v>2533139.644062873</v>
       </c>
     </row>
     <row r="102">
@@ -4958,13 +4958,13 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>3086896.348031463</v>
+        <v>2533139.644062873</v>
       </c>
       <c r="J102" t="n">
-        <v>2161.136133256834</v>
+        <v>1773.451064808294</v>
       </c>
       <c r="K102" t="n">
-        <v>10790.5717114741</v>
+        <v>8854.856756647583</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3089057.484164719</v>
+        <v>2534913.095127682</v>
       </c>
     </row>
     <row r="103">
@@ -5002,13 +5002,13 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>3089057.484164719</v>
+        <v>2534913.095127682</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>10790.5717114741</v>
+        <v>8854.856756647583</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -5017,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3089057.484164719</v>
+        <v>2534913.095127682</v>
       </c>
     </row>
     <row r="104">
@@ -5046,13 +5046,13 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>3089057.484164719</v>
+        <v>2534913.095127682</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>10790.5717114741</v>
+        <v>8854.856756647583</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3089057.484164719</v>
+        <v>2534913.095127682</v>
       </c>
     </row>
     <row r="105">
@@ -5090,13 +5090,13 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>3089057.484164719</v>
+        <v>2534913.095127682</v>
       </c>
       <c r="J105" t="n">
-        <v>2162.649144663475</v>
+        <v>1774.692657898646</v>
       </c>
       <c r="K105" t="n">
-        <v>12953.22085613757</v>
+        <v>10629.54941454623</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3091220.133309383</v>
+        <v>2536687.78778558</v>
       </c>
     </row>
     <row r="106">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>3091220.133309383</v>
+        <v>2536687.78778558</v>
       </c>
       <c r="J106" t="n">
-        <v>2164.163215329871</v>
+        <v>1775.935120228678</v>
       </c>
       <c r="K106" t="n">
-        <v>15117.38407146744</v>
+        <v>12405.48453477491</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3093384.296524713</v>
+        <v>2538463.722905809</v>
       </c>
     </row>
     <row r="107">
@@ -5178,13 +5178,13 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>3093384.296524713</v>
+        <v>2538463.722905809</v>
       </c>
       <c r="J107" t="n">
-        <v>2165.678345996886</v>
+        <v>1777.178452406079</v>
       </c>
       <c r="K107" t="n">
-        <v>17283.06241746433</v>
+        <v>14182.66298718099</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -5193,7 +5193,7 @@
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3095549.97487071</v>
+        <v>2540240.901358215</v>
       </c>
     </row>
     <row r="108">
@@ -5222,13 +5222,13 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>3095549.97487071</v>
+        <v>2540240.901358215</v>
       </c>
       <c r="J108" t="n">
-        <v>2167.194537406787</v>
+        <v>1778.422655040864</v>
       </c>
       <c r="K108" t="n">
-        <v>19450.25695487112</v>
+        <v>15961.08564222185</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -5237,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3097717.169408116</v>
+        <v>2542019.324013256</v>
       </c>
     </row>
     <row r="109">
@@ -5266,13 +5266,13 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>3097717.169408116</v>
+        <v>2542019.324013256</v>
       </c>
       <c r="J109" t="n">
-        <v>2168.711790302768</v>
+        <v>1779.667728741653</v>
       </c>
       <c r="K109" t="n">
-        <v>21618.96874517389</v>
+        <v>17740.7533709635</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3099885.881198419</v>
+        <v>2543798.991741998</v>
       </c>
     </row>
     <row r="110">
@@ -5310,13 +5310,13 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>3099885.881198419</v>
+        <v>2543798.991741998</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>21618.96874517389</v>
+        <v>17740.7533709635</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -5325,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3099885.881198419</v>
+        <v>2543798.991741998</v>
       </c>
     </row>
     <row r="111">
@@ -5354,13 +5354,13 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>3099885.881198419</v>
+        <v>2543798.991741998</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>21618.96874517389</v>
+        <v>17740.7533709635</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3099885.881198419</v>
+        <v>2543798.991741998</v>
       </c>
     </row>
     <row r="112">
@@ -5398,13 +5398,13 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>3099885.881198419</v>
+        <v>2543798.991741998</v>
       </c>
       <c r="J112" t="n">
-        <v>2170.230105427094</v>
+        <v>1780.913674118463</v>
       </c>
       <c r="K112" t="n">
-        <v>23789.19885060098</v>
+        <v>19521.66704508197</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3102056.111303846</v>
+        <v>2545579.905416116</v>
       </c>
     </row>
     <row r="113">
@@ -5442,13 +5442,13 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>3102056.111303846</v>
+        <v>2545579.905416116</v>
       </c>
       <c r="J113" t="n">
-        <v>2171.74948352389</v>
+        <v>1782.160491781775</v>
       </c>
       <c r="K113" t="n">
-        <v>25960.94833412487</v>
+        <v>21303.82753686374</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -5457,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3104227.86078737</v>
+        <v>2547362.065907898</v>
       </c>
     </row>
     <row r="114">
@@ -5486,13 +5486,13 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>3104227.86078737</v>
+        <v>2547362.065907898</v>
       </c>
       <c r="J114" t="n">
-        <v>2173.269925337285</v>
+        <v>1783.408182342071</v>
       </c>
       <c r="K114" t="n">
-        <v>28134.21825946216</v>
+        <v>23087.23571920581</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -5501,7 +5501,7 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3106401.130712708</v>
+        <v>2549145.47409024</v>
       </c>
     </row>
     <row r="115">
@@ -5530,13 +5530,13 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>3106401.130712708</v>
+        <v>2549145.47409024</v>
       </c>
       <c r="J115" t="n">
-        <v>2174.791431611869</v>
+        <v>1784.656746410299</v>
       </c>
       <c r="K115" t="n">
-        <v>30309.00969107402</v>
+        <v>24871.89246561611</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -5545,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3108575.922144319</v>
+        <v>2550930.13083665</v>
       </c>
     </row>
     <row r="116">
@@ -5574,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>3108575.922144319</v>
+        <v>2550930.13083665</v>
       </c>
       <c r="J116" t="n">
-        <v>2176.314003093168</v>
+        <v>1785.906184598804</v>
       </c>
       <c r="K116" t="n">
-        <v>32485.32369416719</v>
+        <v>26657.79865021491</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3110752.236147413</v>
+        <v>2552716.037021249</v>
       </c>
     </row>
     <row r="117">
@@ -5618,13 +5618,13 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>3110752.236147413</v>
+        <v>2552716.037021249</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>32485.32369416719</v>
+        <v>26657.79865021491</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3110752.236147413</v>
+        <v>2552716.037021249</v>
       </c>
     </row>
     <row r="118">
@@ -5662,13 +5662,13 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>3110752.236147413</v>
+        <v>2552716.037021249</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>32485.32369416719</v>
+        <v>26657.79865021491</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>3110752.236147413</v>
+        <v>2552716.037021249</v>
       </c>
     </row>
     <row r="119">
@@ -5706,13 +5706,13 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>3110752.236147413</v>
+        <v>2552716.037021249</v>
       </c>
       <c r="J119" t="n">
-        <v>2177.837640526704</v>
+        <v>1787.156497518532</v>
       </c>
       <c r="K119" t="n">
-        <v>34663.1613346939</v>
+        <v>28444.95514773345</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -5721,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3112930.073787939</v>
+        <v>2554503.193518768</v>
       </c>
     </row>
     <row r="120">
@@ -5750,13 +5750,13 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>3112930.073787939</v>
+        <v>2554503.193518768</v>
       </c>
       <c r="J120" t="n">
-        <v>2179.362344658934</v>
+        <v>1788.407685782295</v>
       </c>
       <c r="K120" t="n">
-        <v>36842.52367935283</v>
+        <v>30233.36283351574</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3115109.436132598</v>
+        <v>2556291.60120455</v>
       </c>
     </row>
     <row r="121">
@@ -5794,13 +5794,13 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>3115109.436132598</v>
+        <v>2556291.60120455</v>
       </c>
       <c r="J121" t="n">
-        <v>2180.88811623631</v>
+        <v>1789.659750003368</v>
       </c>
       <c r="K121" t="n">
-        <v>39023.41179558914</v>
+        <v>32023.02258351911</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3117290.324248835</v>
+        <v>2558081.260954553</v>
       </c>
     </row>
     <row r="122">
@@ -5838,13 +5838,13 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>3117290.324248835</v>
+        <v>2558081.260954553</v>
       </c>
       <c r="J122" t="n">
-        <v>2182.414956006687</v>
+        <v>1790.912690794095</v>
       </c>
       <c r="K122" t="n">
-        <v>41205.82675159583</v>
+        <v>33813.9352743132</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -5853,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3119472.739204841</v>
+        <v>2559872.173645347</v>
       </c>
     </row>
     <row r="123">
@@ -5882,13 +5882,13 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>3119472.739204841</v>
+        <v>2559872.173645347</v>
       </c>
       <c r="J123" t="n">
-        <v>2183.94286471745</v>
+        <v>1792.166508769151</v>
       </c>
       <c r="K123" t="n">
-        <v>43389.76961631328</v>
+        <v>35606.10178308235</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -5897,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3121656.682069559</v>
+        <v>2561664.340154117</v>
       </c>
     </row>
     <row r="124">
@@ -5926,13 +5926,13 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>3121656.682069559</v>
+        <v>2561664.340154117</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>43389.76961631328</v>
+        <v>35606.10178308235</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3121656.682069559</v>
+        <v>2561664.340154117</v>
       </c>
     </row>
     <row r="125">
@@ -5970,13 +5970,13 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>3121656.682069559</v>
+        <v>2561664.340154117</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>43389.76961631328</v>
+        <v>35606.10178308235</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -5985,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3121656.682069559</v>
+        <v>2561664.340154117</v>
       </c>
     </row>
     <row r="126">
@@ -6014,22 +6014,22 @@
         <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>3121656.682069559</v>
+        <v>2561664.340154117</v>
       </c>
       <c r="J126" t="n">
-        <v>2185.471843116917</v>
+        <v>1793.42120454181</v>
       </c>
       <c r="K126" t="n">
-        <v>45575.2414594302</v>
+        <v>37399.52298762416</v>
       </c>
       <c r="L126" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M126" t="n">
-        <v>-30575.2414594302</v>
+        <v>112600.4770123758</v>
       </c>
       <c r="N126" t="n">
-        <v>3108842.153912676</v>
+        <v>2413457.761358658</v>
       </c>
     </row>
     <row r="127">
@@ -6058,13 +6058,13 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>3108842.153912676</v>
+        <v>2413457.761358658</v>
       </c>
       <c r="J127" t="n">
-        <v>2176.50039195409</v>
+        <v>1689.661778727081</v>
       </c>
       <c r="K127" t="n">
-        <v>2176.50039195409</v>
+        <v>1689.661778727081</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3111018.65430463</v>
+        <v>2415147.423137385</v>
       </c>
     </row>
     <row r="128">
@@ -6102,13 +6102,13 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>3111018.65430463</v>
+        <v>2415147.423137385</v>
       </c>
       <c r="J128" t="n">
-        <v>2178.024159878492</v>
+        <v>1690.844710938632</v>
       </c>
       <c r="K128" t="n">
-        <v>4354.524551832583</v>
+        <v>3380.506489665713</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -6117,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3113196.678464508</v>
+        <v>2416838.267848324</v>
       </c>
     </row>
     <row r="129">
@@ -6146,13 +6146,13 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>3113196.678464508</v>
+        <v>2416838.267848324</v>
       </c>
       <c r="J129" t="n">
-        <v>2179.548994592857</v>
+        <v>1692.028471320402</v>
       </c>
       <c r="K129" t="n">
-        <v>6534.073546425439</v>
+        <v>5072.534960986115</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3115376.227459101</v>
+        <v>2418530.296319644</v>
       </c>
     </row>
     <row r="130">
@@ -6190,13 +6190,13 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>3115376.227459101</v>
+        <v>2418530.296319644</v>
       </c>
       <c r="J130" t="n">
-        <v>2181.074896844104</v>
+        <v>1693.213060453534</v>
       </c>
       <c r="K130" t="n">
-        <v>8715.148443269543</v>
+        <v>6765.748021439649</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -6205,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3117557.302355945</v>
+        <v>2420223.509380098</v>
       </c>
     </row>
     <row r="131">
@@ -6234,13 +6234,13 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>3117557.302355945</v>
+        <v>2420223.509380098</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>8715.148443269543</v>
+        <v>6765.748021439649</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3117557.302355945</v>
+        <v>2420223.509380098</v>
       </c>
     </row>
     <row r="132">
@@ -6278,13 +6278,13 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>3117557.302355945</v>
+        <v>2420223.509380098</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>8715.148443269543</v>
+        <v>6765.748021439649</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3117557.302355945</v>
+        <v>2420223.509380098</v>
       </c>
     </row>
     <row r="133">
@@ -6322,13 +6322,13 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>3117557.302355945</v>
+        <v>2420223.509380098</v>
       </c>
       <c r="J133" t="n">
-        <v>2182.601867379155</v>
+        <v>1694.398478916846</v>
       </c>
       <c r="K133" t="n">
-        <v>10897.7503106487</v>
+        <v>8460.146500356495</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -6337,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3119739.904223324</v>
+        <v>2421917.907859015</v>
       </c>
     </row>
     <row r="134">
@@ -6366,13 +6366,13 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>3119739.904223324</v>
+        <v>2421917.907859015</v>
       </c>
       <c r="J134" t="n">
-        <v>2184.129906946793</v>
+        <v>1695.584727291949</v>
       </c>
       <c r="K134" t="n">
-        <v>13081.88021759549</v>
+        <v>10155.73122764844</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3121924.034130271</v>
+        <v>2423613.492586307</v>
       </c>
     </row>
     <row r="135">
@@ -6410,13 +6410,13 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>3121924.034130271</v>
+        <v>2423613.492586307</v>
       </c>
       <c r="J135" t="n">
-        <v>2185.659016294405</v>
+        <v>1696.771806159522</v>
       </c>
       <c r="K135" t="n">
-        <v>15267.5392338899</v>
+        <v>11852.50303380797</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3124109.693146565</v>
+        <v>2425310.264392466</v>
       </c>
     </row>
     <row r="136">
@@ -6454,13 +6454,13 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>3124109.693146565</v>
+        <v>2425310.264392466</v>
       </c>
       <c r="J136" t="n">
-        <v>2187.189196171705</v>
+        <v>1697.959716101177</v>
       </c>
       <c r="K136" t="n">
-        <v>17454.7284300616</v>
+        <v>13550.46274990914</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -6469,7 +6469,7 @@
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3126296.882342737</v>
+        <v>2427008.224108567</v>
       </c>
     </row>
     <row r="137">
@@ -6498,13 +6498,13 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>3126296.882342737</v>
+        <v>2427008.224108567</v>
       </c>
       <c r="J137" t="n">
-        <v>2188.720447327942</v>
+        <v>1699.148457698524</v>
       </c>
       <c r="K137" t="n">
-        <v>19643.44887738954</v>
+        <v>15249.61120760767</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -6513,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3128485.602790065</v>
+        <v>2428707.372566266</v>
       </c>
     </row>
     <row r="138">
@@ -6542,13 +6542,13 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>3128485.602790065</v>
+        <v>2428707.372566266</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>19643.44887738954</v>
+        <v>15249.61120760767</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -6557,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3128485.602790065</v>
+        <v>2428707.372566266</v>
       </c>
     </row>
     <row r="139">
@@ -6586,13 +6586,13 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>3128485.602790065</v>
+        <v>2428707.372566266</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>19643.44887738954</v>
+        <v>15249.61120760767</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>3128485.602790065</v>
+        <v>2428707.372566266</v>
       </c>
     </row>
     <row r="140">
@@ -6630,13 +6630,13 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>3128485.602790065</v>
+        <v>2428707.372566266</v>
       </c>
       <c r="J140" t="n">
-        <v>2190.252770513296</v>
+        <v>1700.33803153364</v>
       </c>
       <c r="K140" t="n">
-        <v>21833.70164790284</v>
+        <v>16949.94923914131</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -6645,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>3130675.855560578</v>
+        <v>2430407.7105978</v>
       </c>
     </row>
     <row r="141">
@@ -6674,13 +6674,13 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>3130675.855560578</v>
+        <v>2430407.7105978</v>
       </c>
       <c r="J141" t="n">
-        <v>2191.786166477948</v>
+        <v>1701.528438189533</v>
       </c>
       <c r="K141" t="n">
-        <v>24025.48781438079</v>
+        <v>18651.47767733084</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -6689,7 +6689,7 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>3132867.641727056</v>
+        <v>2432109.239035989</v>
       </c>
     </row>
     <row r="142">
@@ -6718,13 +6718,13 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>3132867.641727056</v>
+        <v>2432109.239035989</v>
       </c>
       <c r="J142" t="n">
-        <v>2193.32063597301</v>
+        <v>1702.71967824921</v>
       </c>
       <c r="K142" t="n">
-        <v>26218.8084503538</v>
+        <v>20354.19735558005</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3135060.962363029</v>
+        <v>2433811.958714238</v>
       </c>
     </row>
     <row r="143">
@@ -6762,13 +6762,13 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>3135060.962363029</v>
+        <v>2433811.958714238</v>
       </c>
       <c r="J143" t="n">
-        <v>2194.856179750524</v>
+        <v>1703.91175229568</v>
       </c>
       <c r="K143" t="n">
-        <v>28413.66463010432</v>
+        <v>22058.10910787573</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>3137255.81854278</v>
+        <v>2435515.870466534</v>
       </c>
     </row>
     <row r="144">
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>3137255.81854278</v>
+        <v>2435515.870466534</v>
       </c>
       <c r="J144" t="n">
-        <v>2196.392798561603</v>
+        <v>1705.104660913348</v>
       </c>
       <c r="K144" t="n">
-        <v>30610.05742866592</v>
+        <v>23763.21376878908</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -6821,7 +6821,7 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>3139452.211341341</v>
+        <v>2437220.975127447</v>
       </c>
     </row>
     <row r="145">
@@ -6850,13 +6850,13 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>3139452.211341341</v>
+        <v>2437220.975127447</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>30610.05742866592</v>
+        <v>23763.21376878908</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>3139452.211341341</v>
+        <v>2437220.975127447</v>
       </c>
     </row>
     <row r="146">
@@ -6894,13 +6894,13 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>3139452.211341341</v>
+        <v>2437220.975127447</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>30610.05742866592</v>
+        <v>23763.21376878908</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -6909,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>3139452.211341341</v>
+        <v>2437220.975127447</v>
       </c>
     </row>
     <row r="147">
@@ -6938,13 +6938,13 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>3139452.211341341</v>
+        <v>2437220.975127447</v>
       </c>
       <c r="J147" t="n">
-        <v>2197.930493160151</v>
+        <v>1706.298404686619</v>
       </c>
       <c r="K147" t="n">
-        <v>32807.98792182608</v>
+        <v>25469.5121734757</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>3141650.141834502</v>
+        <v>2438927.273532134</v>
       </c>
     </row>
     <row r="148">
@@ -6982,13 +6982,13 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>3141650.141834502</v>
+        <v>2438927.273532134</v>
       </c>
       <c r="J148" t="n">
-        <v>2199.469264298212</v>
+        <v>1707.492984199896</v>
       </c>
       <c r="K148" t="n">
-        <v>35007.45718612429</v>
+        <v>27177.00515767559</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>3143849.6110988</v>
+        <v>2440634.766516334</v>
       </c>
     </row>
     <row r="149">
@@ -7026,13 +7026,13 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>3143849.6110988</v>
+        <v>2440634.766516334</v>
       </c>
       <c r="J149" t="n">
-        <v>2201.009112730157</v>
+        <v>1708.688400038052</v>
       </c>
       <c r="K149" t="n">
-        <v>37208.46629885444</v>
+        <v>28885.69355771365</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -7041,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>3146050.62021153</v>
+        <v>2442343.454916372</v>
       </c>
     </row>
     <row r="150">
@@ -7070,13 +7070,13 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>3146050.62021153</v>
+        <v>2442343.454916372</v>
       </c>
       <c r="J150" t="n">
-        <v>2202.550039209891</v>
+        <v>1709.884652786888</v>
       </c>
       <c r="K150" t="n">
-        <v>39411.01633806434</v>
+        <v>30595.57821050053</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -7085,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>3148253.17025074</v>
+        <v>2444053.339569159</v>
       </c>
     </row>
     <row r="151">
@@ -7114,13 +7114,13 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>3148253.17025074</v>
+        <v>2444053.339569159</v>
       </c>
       <c r="J151" t="n">
-        <v>2204.092044492252</v>
+        <v>1711.081743032206</v>
       </c>
       <c r="K151" t="n">
-        <v>41615.10838255659</v>
+        <v>32306.65995353274</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -7129,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>3150457.262295232</v>
+        <v>2445764.421312191</v>
       </c>
     </row>
     <row r="152">
@@ -7158,13 +7158,13 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>3150457.262295232</v>
+        <v>2445764.421312191</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>41615.10838255659</v>
+        <v>32306.65995353274</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -7173,7 +7173,7 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>3150457.262295232</v>
+        <v>2445764.421312191</v>
       </c>
     </row>
     <row r="153">
@@ -7202,13 +7202,13 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>3150457.262295232</v>
+        <v>2445764.421312191</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>41615.10838255659</v>
+        <v>32306.65995353274</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -7217,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>3150457.262295232</v>
+        <v>2445764.421312191</v>
       </c>
     </row>
     <row r="154">
@@ -7246,22 +7246,22 @@
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>3150457.262295232</v>
+        <v>2445764.421312191</v>
       </c>
       <c r="J154" t="n">
-        <v>2205.635129333008</v>
+        <v>1712.279671360739</v>
       </c>
       <c r="K154" t="n">
-        <v>43820.7435118896</v>
+        <v>34018.93962489348</v>
       </c>
       <c r="L154" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M154" t="n">
-        <v>-28820.7435118896</v>
+        <v>115981.0603751065</v>
       </c>
       <c r="N154" t="n">
-        <v>3137662.897424565</v>
+        <v>2297476.700983552</v>
       </c>
     </row>
     <row r="155">
@@ -7290,13 +7290,13 @@
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>3137662.897424565</v>
+        <v>2297476.700983552</v>
       </c>
       <c r="J155" t="n">
-        <v>2196.67779448675</v>
+        <v>1608.463438358624</v>
       </c>
       <c r="K155" t="n">
-        <v>2196.67779448675</v>
+        <v>1608.463438358624</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>3139859.575219052</v>
+        <v>2299085.16442191</v>
       </c>
     </row>
     <row r="156">
@@ -7334,13 +7334,13 @@
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>3139859.575219052</v>
+        <v>2299085.16442191</v>
       </c>
       <c r="J156" t="n">
-        <v>2198.215688610915</v>
+        <v>1609.58952361159</v>
       </c>
       <c r="K156" t="n">
-        <v>4394.893483097665</v>
+        <v>3218.052961970214</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -7349,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>3142057.790907663</v>
+        <v>2300694.753945522</v>
       </c>
     </row>
     <row r="157">
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>3142057.790907663</v>
+        <v>2300694.753945522</v>
       </c>
       <c r="J157" t="n">
-        <v>2199.754659414291</v>
+        <v>1610.716397237033</v>
       </c>
       <c r="K157" t="n">
-        <v>6594.648142511956</v>
+        <v>4828.769359207246</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>3144257.545567077</v>
+        <v>2302305.470342759</v>
       </c>
     </row>
     <row r="158">
@@ -7422,13 +7422,13 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>3144257.545567077</v>
+        <v>2302305.470342759</v>
       </c>
       <c r="J158" t="n">
-        <v>2201.29470765125</v>
+        <v>1611.844059786759</v>
       </c>
       <c r="K158" t="n">
-        <v>8795.942850163206</v>
+        <v>6440.613418994006</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>3146458.840274728</v>
+        <v>2303917.314402546</v>
       </c>
     </row>
     <row r="159">
@@ -7466,13 +7466,13 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>3146458.840274728</v>
+        <v>2303917.314402546</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>8795.942850163206</v>
+        <v>6440.613418994006</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -7481,7 +7481,7 @@
         <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>3146458.840274728</v>
+        <v>2303917.314402546</v>
       </c>
     </row>
     <row r="160">
@@ -7510,13 +7510,13 @@
         <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>3146458.840274728</v>
+        <v>2303917.314402546</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>8795.942850163206</v>
+        <v>6440.613418994006</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
         <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>3146458.840274728</v>
+        <v>2303917.314402546</v>
       </c>
     </row>
     <row r="161">
@@ -7554,13 +7554,13 @@
         <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>3146458.840274728</v>
+        <v>2303917.314402546</v>
       </c>
       <c r="J161" t="n">
-        <v>2202.835834076162</v>
+        <v>1612.972511813045</v>
       </c>
       <c r="K161" t="n">
-        <v>10998.77868423937</v>
+        <v>8053.58593080705</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>3148661.676108805</v>
+        <v>2305530.286914359</v>
       </c>
     </row>
     <row r="162">
@@ -7598,13 +7598,13 @@
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>3148661.676108805</v>
+        <v>2305530.286914359</v>
       </c>
       <c r="J162" t="n">
-        <v>2204.378039443865</v>
+        <v>1614.101753868628</v>
       </c>
       <c r="K162" t="n">
-        <v>13203.15672368323</v>
+        <v>9667.687684675679</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>3150866.054148248</v>
+        <v>2307144.388668227</v>
       </c>
     </row>
     <row r="163">
@@ -7642,13 +7642,13 @@
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>3150866.054148248</v>
+        <v>2307144.388668227</v>
       </c>
       <c r="J163" t="n">
-        <v>2205.921324509196</v>
+        <v>1615.231786506716</v>
       </c>
       <c r="K163" t="n">
-        <v>15409.07804819243</v>
+        <v>11282.91947118239</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -7657,7 +7657,7 @@
         <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>3153071.975472758</v>
+        <v>2308759.620454734</v>
       </c>
     </row>
     <row r="164">
@@ -7686,13 +7686,13 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>3153071.975472758</v>
+        <v>2308759.620454734</v>
       </c>
       <c r="J164" t="n">
-        <v>2207.465690028388</v>
+        <v>1616.362610280514</v>
       </c>
       <c r="K164" t="n">
-        <v>17616.54373822082</v>
+        <v>12899.28208146291</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -7701,7 +7701,7 @@
         <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>3155279.441162786</v>
+        <v>2310375.983065015</v>
       </c>
     </row>
     <row r="165">
@@ -7730,13 +7730,13 @@
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>3155279.441162786</v>
+        <v>2310375.983065015</v>
       </c>
       <c r="J165" t="n">
-        <v>2209.011136758141</v>
+        <v>1617.494225743692</v>
       </c>
       <c r="K165" t="n">
-        <v>19825.55487497896</v>
+        <v>14516.7763072066</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -7745,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>3157488.452299544</v>
+        <v>2311993.477290758</v>
       </c>
     </row>
     <row r="166">
@@ -7774,13 +7774,13 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>3157488.452299544</v>
+        <v>2311993.477290758</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>19825.55487497896</v>
+        <v>14516.7763072066</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>3157488.452299544</v>
+        <v>2311993.477290758</v>
       </c>
     </row>
     <row r="167">
@@ -7818,13 +7818,13 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>3157488.452299544</v>
+        <v>2311993.477290758</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>19825.55487497896</v>
+        <v>14516.7763072066</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>3157488.452299544</v>
+        <v>2311993.477290758</v>
       </c>
     </row>
     <row r="168">
@@ -7862,13 +7862,13 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>3157488.452299544</v>
+        <v>2311993.477290758</v>
       </c>
       <c r="J168" t="n">
-        <v>2210.557665454689</v>
+        <v>1618.62663345132</v>
       </c>
       <c r="K168" t="n">
-        <v>22036.11254043365</v>
+        <v>16135.40294065792</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -7877,7 +7877,7 @@
         <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>3159699.009964999</v>
+        <v>2313612.10392421</v>
       </c>
     </row>
     <row r="169">
@@ -7906,13 +7906,13 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>3159699.009964999</v>
+        <v>2313612.10392421</v>
       </c>
       <c r="J169" t="n">
-        <v>2212.105276876595</v>
+        <v>1619.759833957069</v>
       </c>
       <c r="K169" t="n">
-        <v>24248.21781731024</v>
+        <v>17755.16277461499</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -7921,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>3161911.115241875</v>
+        <v>2315231.863758167</v>
       </c>
     </row>
     <row r="170">
@@ -7950,13 +7950,13 @@
         <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>3161911.115241875</v>
+        <v>2315231.863758167</v>
       </c>
       <c r="J170" t="n">
-        <v>2213.653971780557</v>
+        <v>1620.893827816937</v>
       </c>
       <c r="K170" t="n">
-        <v>26461.8717890908</v>
+        <v>19376.05660243193</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -7965,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>3164124.769213656</v>
+        <v>2316852.757585984</v>
       </c>
     </row>
     <row r="171">
@@ -7994,13 +7994,13 @@
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>3164124.769213656</v>
+        <v>2316852.757585984</v>
       </c>
       <c r="J171" t="n">
-        <v>2215.203750926536</v>
+        <v>1622.028615585994</v>
       </c>
       <c r="K171" t="n">
-        <v>28677.07554001734</v>
+        <v>20998.08521801792</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -8009,7 +8009,7 @@
         <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>3166339.972964582</v>
+        <v>2318474.78620157</v>
       </c>
     </row>
     <row r="172">
@@ -8038,13 +8038,13 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>3166339.972964582</v>
+        <v>2318474.78620157</v>
       </c>
       <c r="J172" t="n">
-        <v>2216.754615072627</v>
+        <v>1623.164197819773</v>
       </c>
       <c r="K172" t="n">
-        <v>30893.83015508996</v>
+        <v>22621.24941583769</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -8053,7 +8053,7 @@
         <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3168556.727579655</v>
+        <v>2320097.950399389</v>
       </c>
     </row>
     <row r="173">
@@ -8082,13 +8082,13 @@
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>3168556.727579655</v>
+        <v>2320097.950399389</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>30893.83015508996</v>
+        <v>22621.24941583769</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>3168556.727579655</v>
+        <v>2320097.950399389</v>
       </c>
     </row>
     <row r="174">
@@ -8126,13 +8126,13 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>3168556.727579655</v>
+        <v>2320097.950399389</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>30893.83015508996</v>
+        <v>22621.24941583769</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>3168556.727579655</v>
+        <v>2320097.950399389</v>
       </c>
     </row>
     <row r="175">
@@ -8170,13 +8170,13 @@
         <v>0</v>
       </c>
       <c r="I175" t="n">
-        <v>3168556.727579655</v>
+        <v>2320097.950399389</v>
       </c>
       <c r="J175" t="n">
-        <v>2218.306564978324</v>
+        <v>1624.30057507474</v>
       </c>
       <c r="K175" t="n">
-        <v>33112.13672006829</v>
+        <v>24245.54999091243</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -8185,7 +8185,7 @@
         <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>3170775.034144633</v>
+        <v>2321722.250974464</v>
       </c>
     </row>
     <row r="176">
@@ -8214,13 +8214,13 @@
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>3170775.034144633</v>
+        <v>2321722.250974464</v>
       </c>
       <c r="J176" t="n">
-        <v>2219.859601404518</v>
+        <v>1625.437747907359</v>
       </c>
       <c r="K176" t="n">
-        <v>35331.9963214728</v>
+        <v>25870.98773881979</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -8229,7 +8229,7 @@
         <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>3172994.893746038</v>
+        <v>2323347.688722372</v>
       </c>
     </row>
     <row r="177">
@@ -8258,13 +8258,13 @@
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>3172994.893746038</v>
+        <v>2323347.688722372</v>
       </c>
       <c r="J177" t="n">
-        <v>2221.413725111634</v>
+        <v>1626.575716874562</v>
       </c>
       <c r="K177" t="n">
-        <v>37553.41004658444</v>
+        <v>27497.56345569436</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -8273,7 +8273,7 @@
         <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>3175216.30747115</v>
+        <v>2324974.264439246</v>
       </c>
     </row>
     <row r="178">
@@ -8302,13 +8302,13 @@
         <v>0</v>
       </c>
       <c r="I178" t="n">
-        <v>3175216.30747115</v>
+        <v>2324974.264439246</v>
       </c>
       <c r="J178" t="n">
-        <v>2222.968936860561</v>
+        <v>1627.714482533745</v>
       </c>
       <c r="K178" t="n">
-        <v>39776.378983445</v>
+        <v>29125.2779382281</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -8317,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>3177439.27640801</v>
+        <v>2326601.97892178</v>
       </c>
     </row>
     <row r="179">
@@ -8346,13 +8346,13 @@
         <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>3177439.27640801</v>
+        <v>2326601.97892178</v>
       </c>
       <c r="J179" t="n">
-        <v>2224.525237413123</v>
+        <v>1628.854045443237</v>
       </c>
       <c r="K179" t="n">
-        <v>42000.90422085812</v>
+        <v>30754.13198367134</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>3179663.801645423</v>
+        <v>2328230.832967223</v>
       </c>
     </row>
     <row r="180">
@@ -8390,13 +8390,13 @@
         <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>3179663.801645423</v>
+        <v>2328230.832967223</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>42000.90422085812</v>
+        <v>30754.13198367134</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -8405,7 +8405,7 @@
         <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>3179663.801645423</v>
+        <v>2328230.832967223</v>
       </c>
     </row>
     <row r="181">
@@ -8434,13 +8434,13 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>3179663.801645423</v>
+        <v>2328230.832967223</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>42000.90422085812</v>
+        <v>30754.13198367134</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -8449,7 +8449,7 @@
         <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>3179663.801645423</v>
+        <v>2328230.832967223</v>
       </c>
     </row>
     <row r="182">
@@ -8478,13 +8478,13 @@
         <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>3179663.801645423</v>
+        <v>2328230.832967223</v>
       </c>
       <c r="J182" t="n">
-        <v>2226.082627532072</v>
+        <v>1629.994406160433</v>
       </c>
       <c r="K182" t="n">
-        <v>44226.9868483902</v>
+        <v>32384.12638983177</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -8493,7 +8493,7 @@
         <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>3181889.884272955</v>
+        <v>2329860.827373384</v>
       </c>
     </row>
     <row r="183">
@@ -8522,13 +8522,13 @@
         <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>3181889.884272955</v>
+        <v>2329860.827373384</v>
       </c>
       <c r="J183" t="n">
-        <v>2227.641107979231</v>
+        <v>1631.135565244127</v>
       </c>
       <c r="K183" t="n">
-        <v>46454.62795636943</v>
+        <v>34015.2619550759</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
         <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>3184117.525380935</v>
+        <v>2331491.962938628</v>
       </c>
     </row>
     <row r="184">
@@ -8566,22 +8566,22 @@
         <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>3184117.525380935</v>
+        <v>2331491.962938628</v>
       </c>
       <c r="J184" t="n">
-        <v>2229.200679519214</v>
+        <v>1632.277523253113</v>
       </c>
       <c r="K184" t="n">
-        <v>48683.82863588864</v>
+        <v>35647.53947832901</v>
       </c>
       <c r="L184" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M184" t="n">
-        <v>-33683.82863588864</v>
+        <v>114352.460521671</v>
       </c>
       <c r="N184" t="n">
-        <v>3171346.726060454</v>
+        <v>2183124.240461881</v>
       </c>
     </row>
     <row r="185">
@@ -8610,13 +8610,13 @@
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>3171346.726060454</v>
+        <v>2183124.240461881</v>
       </c>
       <c r="J185" t="n">
-        <v>2220.259842914995</v>
+        <v>1528.405280747451</v>
       </c>
       <c r="K185" t="n">
-        <v>2220.259842914995</v>
+        <v>1528.405280747451</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>3173566.985903369</v>
+        <v>2184652.645742628</v>
       </c>
     </row>
     <row r="186">
@@ -8658,13 +8658,13 @@
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>3173566.985903369</v>
+        <v>2184652.645742628</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>2220.259842914995</v>
+        <v>1528.405280747451</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -8673,7 +8673,7 @@
         <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>3173566.985903369</v>
+        <v>2184652.645742628</v>
       </c>
     </row>
     <row r="187">
@@ -8702,13 +8702,13 @@
         <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>3173566.985903369</v>
+        <v>2184652.645742628</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>2220.259842914995</v>
+        <v>1528.405280747451</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -8717,7 +8717,7 @@
         <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>3173566.985903369</v>
+        <v>2184652.645742628</v>
       </c>
     </row>
     <row r="188">
@@ -8746,13 +8746,13 @@
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>3173566.985903369</v>
+        <v>2184652.645742628</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>2220.259842914995</v>
+        <v>1528.405280747451</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -8761,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>3173566.985903369</v>
+        <v>2184652.645742628</v>
       </c>
     </row>
     <row r="189">
@@ -8790,13 +8790,13 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>3173566.985903369</v>
+        <v>2184652.645742628</v>
       </c>
       <c r="J189" t="n">
-        <v>2221.814246830996</v>
+        <v>1529.475317284465</v>
       </c>
       <c r="K189" t="n">
-        <v>4442.074089745991</v>
+        <v>3057.880598031916</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
         <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>3175788.8001502</v>
+        <v>2186182.121059913</v>
       </c>
     </row>
     <row r="190">
@@ -8834,13 +8834,13 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>3175788.8001502</v>
+        <v>2186182.121059913</v>
       </c>
       <c r="J190" t="n">
-        <v>2223.369738985319</v>
+        <v>1530.546102954075</v>
       </c>
       <c r="K190" t="n">
-        <v>6665.44382873131</v>
+        <v>4588.42670098599</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>3178012.169889185</v>
+        <v>2187712.667162867</v>
       </c>
     </row>
     <row r="191">
@@ -8878,13 +8878,13 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>3178012.169889185</v>
+        <v>2187712.667162867</v>
       </c>
       <c r="J191" t="n">
-        <v>2224.926320139319</v>
+        <v>1531.617638280615</v>
       </c>
       <c r="K191" t="n">
-        <v>8890.370148870628</v>
+        <v>6120.044339266606</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
         <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>3180237.096209324</v>
+        <v>2189244.284801147</v>
       </c>
     </row>
     <row r="192">
@@ -8922,13 +8922,13 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>3180237.096209324</v>
+        <v>2189244.284801147</v>
       </c>
       <c r="J192" t="n">
-        <v>2226.483991056215</v>
+        <v>1532.689923789352</v>
       </c>
       <c r="K192" t="n">
-        <v>11116.85413992684</v>
+        <v>7652.734263055958</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>3182463.580200381</v>
+        <v>2190776.974724937</v>
       </c>
     </row>
     <row r="193">
@@ -8966,13 +8966,13 @@
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>3182463.580200381</v>
+        <v>2190776.974724937</v>
       </c>
       <c r="J193" t="n">
-        <v>2228.042752498295</v>
+        <v>1533.762960005086</v>
       </c>
       <c r="K193" t="n">
-        <v>13344.89689242514</v>
+        <v>9186.497223061044</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -8981,7 +8981,7 @@
         <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>3184691.622952879</v>
+        <v>2192310.737684942</v>
       </c>
     </row>
     <row r="194">
@@ -9010,13 +9010,13 @@
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>3184691.622952879</v>
+        <v>2192310.737684942</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>13344.89689242514</v>
+        <v>9186.497223061044</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -9025,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>3184691.622952879</v>
+        <v>2192310.737684942</v>
       </c>
     </row>
     <row r="195">
@@ -9054,13 +9054,13 @@
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>3184691.622952879</v>
+        <v>2192310.737684942</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>13344.89689242514</v>
+        <v>9186.497223061044</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>3184691.622952879</v>
+        <v>2192310.737684942</v>
       </c>
     </row>
     <row r="196">
@@ -9098,13 +9098,13 @@
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>3184691.622952879</v>
+        <v>2192310.737684942</v>
       </c>
       <c r="J196" t="n">
-        <v>2229.602605229244</v>
+        <v>1534.836747453082</v>
       </c>
       <c r="K196" t="n">
-        <v>15574.49949765438</v>
+        <v>10721.33397051413</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>3186921.225558108</v>
+        <v>2193845.574432395</v>
       </c>
     </row>
     <row r="197">
@@ -9142,13 +9142,13 @@
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>3186921.225558108</v>
+        <v>2193845.574432395</v>
       </c>
       <c r="J197" t="n">
-        <v>2231.163550013211</v>
+        <v>1535.911286660004</v>
       </c>
       <c r="K197" t="n">
-        <v>17805.66304766759</v>
+        <v>12257.24525717413</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -9157,7 +9157,7 @@
         <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>3189152.389108121</v>
+        <v>2195381.485719055</v>
       </c>
     </row>
     <row r="198">
@@ -9186,13 +9186,13 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>3189152.389108121</v>
+        <v>2195381.485719055</v>
       </c>
       <c r="J198" t="n">
-        <v>2232.725587614346</v>
+        <v>1536.986578152049</v>
       </c>
       <c r="K198" t="n">
-        <v>20038.38863528194</v>
+        <v>13794.23183532618</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -9201,7 +9201,7 @@
         <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>3191385.114695736</v>
+        <v>2196918.472297207</v>
       </c>
     </row>
     <row r="199">
@@ -9230,13 +9230,13 @@
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>3191385.114695736</v>
+        <v>2196918.472297207</v>
       </c>
       <c r="J199" t="n">
-        <v>2234.288718798198</v>
+        <v>1538.062622455414</v>
       </c>
       <c r="K199" t="n">
-        <v>22272.67735408014</v>
+        <v>15332.29445778159</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -9245,7 +9245,7 @@
         <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>3193619.403414534</v>
+        <v>2198456.534919662</v>
       </c>
     </row>
     <row r="200">
@@ -9274,13 +9274,13 @@
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>3193619.403414534</v>
+        <v>2198456.534919662</v>
       </c>
       <c r="J200" t="n">
-        <v>2235.852944330312</v>
+        <v>1539.139420097228</v>
       </c>
       <c r="K200" t="n">
-        <v>24508.53029841045</v>
+        <v>16871.43387787882</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>3195855.256358864</v>
+        <v>2199995.67433976</v>
       </c>
     </row>
     <row r="201">
@@ -9318,13 +9318,13 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>3195855.256358864</v>
+        <v>2199995.67433976</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>24508.53029841045</v>
+        <v>16871.43387787882</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -9333,7 +9333,7 @@
         <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>3195855.256358864</v>
+        <v>2199995.67433976</v>
       </c>
     </row>
     <row r="202">
@@ -9362,13 +9362,13 @@
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>3195855.256358864</v>
+        <v>2199995.67433976</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>24508.53029841045</v>
+        <v>16871.43387787882</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -9377,7 +9377,7 @@
         <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>3195855.256358864</v>
+        <v>2199995.67433976</v>
       </c>
     </row>
     <row r="203">
@@ -9406,13 +9406,13 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>3195855.256358864</v>
+        <v>2199995.67433976</v>
       </c>
       <c r="J203" t="n">
-        <v>2237.418264976703</v>
+        <v>1540.216971605085</v>
       </c>
       <c r="K203" t="n">
-        <v>26745.94856338715</v>
+        <v>18411.65084948391</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>3198092.674623841</v>
+        <v>2201535.891311365</v>
       </c>
     </row>
     <row r="204">
@@ -9454,13 +9454,13 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>3198092.674623841</v>
+        <v>2201535.891311365</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>26745.94856338715</v>
+        <v>18411.65084948391</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -9469,7 +9469,7 @@
         <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>3198092.674623841</v>
+        <v>2201535.891311365</v>
       </c>
     </row>
     <row r="205">
@@ -9498,13 +9498,13 @@
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>3198092.674623841</v>
+        <v>2201535.891311365</v>
       </c>
       <c r="J205" t="n">
-        <v>2238.984681504313</v>
+        <v>1541.295277507044</v>
       </c>
       <c r="K205" t="n">
-        <v>28984.93324489146</v>
+        <v>19952.94612699095</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -9513,7 +9513,7 @@
         <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>3200331.659305345</v>
+        <v>2203077.186588872</v>
       </c>
     </row>
     <row r="206">
@@ -9542,13 +9542,13 @@
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>3200331.659305345</v>
+        <v>2203077.186588872</v>
       </c>
       <c r="J206" t="n">
-        <v>2240.552194679622</v>
+        <v>1542.374338330701</v>
       </c>
       <c r="K206" t="n">
-        <v>31225.48543957109</v>
+        <v>21495.32046532165</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -9557,7 +9557,7 @@
         <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>3202572.211500025</v>
+        <v>2204619.560927202</v>
       </c>
     </row>
     <row r="207">
@@ -9586,13 +9586,13 @@
         <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>3202572.211500025</v>
+        <v>2204619.560927202</v>
       </c>
       <c r="J207" t="n">
-        <v>2242.12080527097</v>
+        <v>1543.454154605046</v>
       </c>
       <c r="K207" t="n">
-        <v>33467.60624484206</v>
+        <v>23038.7746199267</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -9601,7 +9601,7 @@
         <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>3204814.332305296</v>
+        <v>2206163.015081808</v>
       </c>
     </row>
     <row r="208">
@@ -9630,13 +9630,13 @@
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>3204814.332305296</v>
+        <v>2206163.015081808</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>33467.60624484206</v>
+        <v>23038.7746199267</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -9645,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>3204814.332305296</v>
+        <v>2206163.015081808</v>
       </c>
     </row>
     <row r="209">
@@ -9674,13 +9674,13 @@
         <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>3204814.332305296</v>
+        <v>2206163.015081808</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>33467.60624484206</v>
+        <v>23038.7746199267</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>3204814.332305296</v>
+        <v>2206163.015081808</v>
       </c>
     </row>
     <row r="210">
@@ -9718,13 +9718,13 @@
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>3204814.332305296</v>
+        <v>2206163.015081808</v>
       </c>
       <c r="J210" t="n">
-        <v>2243.690514046699</v>
+        <v>1544.534726858605</v>
       </c>
       <c r="K210" t="n">
-        <v>35711.29675888875</v>
+        <v>24583.3093467853</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -9733,7 +9733,7 @@
         <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>3207058.022819343</v>
+        <v>2207707.549808666</v>
       </c>
     </row>
     <row r="211">
@@ -9762,13 +9762,13 @@
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>3207058.022819343</v>
+        <v>2207707.549808666</v>
       </c>
       <c r="J211" t="n">
-        <v>2245.261321775615</v>
+        <v>1545.616055620834</v>
       </c>
       <c r="K211" t="n">
-        <v>37956.55808066437</v>
+        <v>26128.92540240614</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -9777,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>3209303.284141118</v>
+        <v>2209253.165864287</v>
       </c>
     </row>
     <row r="212">
@@ -9806,13 +9806,13 @@
         <v>0</v>
       </c>
       <c r="I212" t="n">
-        <v>3209303.284141118</v>
+        <v>2209253.165864287</v>
       </c>
       <c r="J212" t="n">
-        <v>2246.833229226992</v>
+        <v>1546.698141421657</v>
       </c>
       <c r="K212" t="n">
-        <v>40203.39130989136</v>
+        <v>27675.62354382779</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -9821,7 +9821,7 @@
         <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>3211550.117370345</v>
+        <v>2210799.864005709</v>
       </c>
     </row>
     <row r="213">
@@ -9850,13 +9850,13 @@
         <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>3211550.117370345</v>
+        <v>2210799.864005709</v>
       </c>
       <c r="J213" t="n">
-        <v>2248.406237171032</v>
+        <v>1547.78098479053</v>
       </c>
       <c r="K213" t="n">
-        <v>42451.79754706239</v>
+        <v>29223.40452861832</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -9865,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>3213798.523607516</v>
+        <v>2212347.644990499</v>
       </c>
     </row>
     <row r="214">
@@ -9898,13 +9898,13 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>3213798.523607516</v>
+        <v>2212347.644990499</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>42451.79754706239</v>
+        <v>29223.40452861832</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -9913,7 +9913,7 @@
         <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>3213798.523607516</v>
+        <v>2212347.644990499</v>
       </c>
     </row>
     <row r="215">
@@ -9942,13 +9942,13 @@
         <v>0</v>
       </c>
       <c r="I215" t="n">
-        <v>3213798.523607516</v>
+        <v>2212347.644990499</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>42451.79754706239</v>
+        <v>29223.40452861832</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -9957,7 +9957,7 @@
         <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>3213798.523607516</v>
+        <v>2212347.644990499</v>
       </c>
     </row>
     <row r="216">
@@ -9986,13 +9986,13 @@
         <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>3213798.523607516</v>
+        <v>2212347.644990499</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
       </c>
       <c r="K216" t="n">
-        <v>42451.79754706239</v>
+        <v>29223.40452861832</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>3213798.523607516</v>
+        <v>2212347.644990499</v>
       </c>
     </row>
     <row r="217">
@@ -10030,22 +10030,22 @@
         <v>1</v>
       </c>
       <c r="I217" t="n">
-        <v>3213798.523607516</v>
+        <v>2212347.644990499</v>
       </c>
       <c r="J217" t="n">
-        <v>2249.980346377473</v>
+        <v>1548.864586257841</v>
       </c>
       <c r="K217" t="n">
-        <v>44701.77789343987</v>
+        <v>30772.26911487617</v>
       </c>
       <c r="L217" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M217" t="n">
-        <v>-29701.77789343987</v>
+        <v>119227.7308851238</v>
       </c>
       <c r="N217" t="n">
-        <v>3201048.503953894</v>
+        <v>2063896.509576757</v>
       </c>
     </row>
     <row r="218">
@@ -10074,13 +10074,13 @@
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>3201048.503953894</v>
+        <v>2063896.509576757</v>
       </c>
       <c r="J218" t="n">
-        <v>2241.054057618137</v>
+        <v>1444.933946354548</v>
       </c>
       <c r="K218" t="n">
-        <v>2241.054057618137</v>
+        <v>1444.933946354548</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>3203289.558011512</v>
+        <v>2065341.443523112</v>
       </c>
     </row>
     <row r="219">
@@ -10118,13 +10118,13 @@
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>3203289.558011512</v>
+        <v>2065341.443523112</v>
       </c>
       <c r="J219" t="n">
-        <v>2242.623019563965</v>
+        <v>1445.945544610498</v>
       </c>
       <c r="K219" t="n">
-        <v>4483.677077182103</v>
+        <v>2890.879490965046</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -10133,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>3205532.181031076</v>
+        <v>2066787.389067722</v>
       </c>
     </row>
     <row r="220">
@@ -10162,13 +10162,13 @@
         <v>0</v>
       </c>
       <c r="I220" t="n">
-        <v>3205532.181031076</v>
+        <v>2066787.389067722</v>
       </c>
       <c r="J220" t="n">
-        <v>2244.193079939578</v>
+        <v>1446.957851086278</v>
       </c>
       <c r="K220" t="n">
-        <v>6727.870157121681</v>
+        <v>4337.837342051324</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -10177,7 +10177,7 @@
         <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>3207776.374111015</v>
+        <v>2068234.346918808</v>
       </c>
     </row>
     <row r="221">
@@ -10206,13 +10206,13 @@
         <v>0</v>
       </c>
       <c r="I221" t="n">
-        <v>3207776.374111015</v>
+        <v>2068234.346918808</v>
       </c>
       <c r="J221" t="n">
-        <v>2245.764239515178</v>
+        <v>1447.970866277814</v>
       </c>
       <c r="K221" t="n">
-        <v>8973.634396636859</v>
+        <v>5785.808208329137</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
@@ -10221,7 +10221,7 @@
         <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>3210022.138350531</v>
+        <v>2069682.317785086</v>
       </c>
     </row>
     <row r="222">
@@ -10250,13 +10250,13 @@
         <v>0</v>
       </c>
       <c r="I222" t="n">
-        <v>3210022.138350531</v>
+        <v>2069682.317785086</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>8973.634396636859</v>
+        <v>5785.808208329137</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -10265,7 +10265,7 @@
         <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>3210022.138350531</v>
+        <v>2069682.317785086</v>
       </c>
     </row>
     <row r="223">
@@ -10294,13 +10294,13 @@
         <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>3210022.138350531</v>
+        <v>2069682.317785086</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>8973.634396636859</v>
+        <v>5785.808208329137</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -10309,7 +10309,7 @@
         <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>3210022.138350531</v>
+        <v>2069682.317785086</v>
       </c>
     </row>
     <row r="224">
@@ -10338,13 +10338,13 @@
         <v>0</v>
       </c>
       <c r="I224" t="n">
-        <v>3210022.138350531</v>
+        <v>2069682.317785086</v>
       </c>
       <c r="J224" t="n">
-        <v>2247.336499059107</v>
+        <v>1448.98459068127</v>
       </c>
       <c r="K224" t="n">
-        <v>11220.97089569597</v>
+        <v>7234.792799010407</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -10353,7 +10353,7 @@
         <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>3212269.47484959</v>
+        <v>2071131.302375767</v>
       </c>
     </row>
     <row r="225">
@@ -10382,13 +10382,13 @@
         <v>0</v>
       </c>
       <c r="I225" t="n">
-        <v>3212269.47484959</v>
+        <v>2071131.302375767</v>
       </c>
       <c r="J225" t="n">
-        <v>2248.909859342035</v>
+        <v>1449.999024793273</v>
       </c>
       <c r="K225" t="n">
-        <v>13469.880755038</v>
+        <v>8684.79182380368</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
@@ -10397,7 +10397,7 @@
         <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>3214518.384708932</v>
+        <v>2072581.301400561</v>
       </c>
     </row>
     <row r="226">
@@ -10426,13 +10426,13 @@
         <v>0</v>
       </c>
       <c r="I226" t="n">
-        <v>3214518.384708932</v>
+        <v>2072581.301400561</v>
       </c>
       <c r="J226" t="n">
-        <v>2250.484321134631</v>
+        <v>1451.014169110451</v>
       </c>
       <c r="K226" t="n">
-        <v>15720.36507617263</v>
+        <v>10135.80599291413</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -10441,7 +10441,7 @@
         <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>3216768.869030066</v>
+        <v>2074032.315569671</v>
       </c>
     </row>
     <row r="227">
@@ -10470,13 +10470,13 @@
         <v>0</v>
       </c>
       <c r="I227" t="n">
-        <v>3216768.869030066</v>
+        <v>2074032.315569671</v>
       </c>
       <c r="J227" t="n">
-        <v>2252.059885208029</v>
+        <v>1452.030024130363</v>
       </c>
       <c r="K227" t="n">
-        <v>17972.42496138066</v>
+        <v>11587.83601704449</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -10485,7 +10485,7 @@
         <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>3219020.928915274</v>
+        <v>2075484.345593801</v>
       </c>
     </row>
     <row r="228">
@@ -10514,13 +10514,13 @@
         <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>3219020.928915274</v>
+        <v>2075484.345593801</v>
       </c>
       <c r="J228" t="n">
-        <v>2253.636552333366</v>
+        <v>1453.046590350103</v>
       </c>
       <c r="K228" t="n">
-        <v>20226.06151371403</v>
+        <v>13040.8826073946</v>
       </c>
       <c r="L228" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
         <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>3221274.565467608</v>
+        <v>2076937.392184152</v>
       </c>
     </row>
     <row r="229">
@@ -10558,13 +10558,13 @@
         <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>3221274.565467608</v>
+        <v>2076937.392184152</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>20226.06151371403</v>
+        <v>13040.8826073946</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
@@ -10573,7 +10573,7 @@
         <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>3221274.565467608</v>
+        <v>2076937.392184152</v>
       </c>
     </row>
     <row r="230">
@@ -10602,13 +10602,13 @@
         <v>0</v>
       </c>
       <c r="I230" t="n">
-        <v>3221274.565467608</v>
+        <v>2076937.392184152</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>20226.06151371403</v>
+        <v>13040.8826073946</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -10617,7 +10617,7 @@
         <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>3221274.565467608</v>
+        <v>2076937.392184152</v>
       </c>
     </row>
     <row r="231">
@@ -10646,13 +10646,13 @@
         <v>0</v>
       </c>
       <c r="I231" t="n">
-        <v>3221274.565467608</v>
+        <v>2076937.392184152</v>
       </c>
       <c r="J231" t="n">
-        <v>2255.214323283639</v>
+        <v>1454.06386826816</v>
       </c>
       <c r="K231" t="n">
-        <v>22481.27583699767</v>
+        <v>14494.94647566276</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -10661,7 +10661,7 @@
         <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>3223529.779790891</v>
+        <v>2078391.45605242</v>
       </c>
     </row>
     <row r="232">
@@ -10690,13 +10690,13 @@
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>3223529.779790891</v>
+        <v>2078391.45605242</v>
       </c>
       <c r="J232" t="n">
-        <v>2256.793198831379</v>
+        <v>1455.081858382327</v>
       </c>
       <c r="K232" t="n">
-        <v>24738.06903582904</v>
+        <v>15950.02833404508</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -10705,7 +10705,7 @@
         <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>3225786.572989723</v>
+        <v>2079846.537910802</v>
       </c>
     </row>
     <row r="233">
@@ -10734,13 +10734,13 @@
         <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>3225786.572989723</v>
+        <v>2079846.537910802</v>
       </c>
       <c r="J233" t="n">
-        <v>2258.373179750051</v>
+        <v>1456.100561191328</v>
       </c>
       <c r="K233" t="n">
-        <v>26996.4422155791</v>
+        <v>17406.12889523641</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -10749,7 +10749,7 @@
         <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>3228044.946169473</v>
+        <v>2081302.638471993</v>
       </c>
     </row>
     <row r="234">
@@ -10778,13 +10778,13 @@
         <v>0</v>
       </c>
       <c r="I234" t="n">
-        <v>3228044.946169473</v>
+        <v>2081302.638471993</v>
       </c>
       <c r="J234" t="n">
-        <v>2259.954266813118</v>
+        <v>1457.119977194117</v>
       </c>
       <c r="K234" t="n">
-        <v>29256.39648239221</v>
+        <v>18863.24887243053</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -10793,7 +10793,7 @@
         <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>3230304.900436286</v>
+        <v>2082759.758449188</v>
       </c>
     </row>
     <row r="235">
@@ -10822,13 +10822,13 @@
         <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>3230304.900436286</v>
+        <v>2082759.758449188</v>
       </c>
       <c r="J235" t="n">
-        <v>2261.53646079544</v>
+        <v>1458.140106890351</v>
       </c>
       <c r="K235" t="n">
-        <v>31517.93294318765</v>
+        <v>20321.38897932088</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>3232566.436897081</v>
+        <v>2084217.898556078</v>
       </c>
     </row>
     <row r="236">
@@ -10866,13 +10866,13 @@
         <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>3232566.436897081</v>
+        <v>2084217.898556078</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>31517.93294318765</v>
+        <v>20321.38897932088</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -10881,7 +10881,7 @@
         <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>3232566.436897081</v>
+        <v>2084217.898556078</v>
       </c>
     </row>
     <row r="237">
@@ -10910,13 +10910,13 @@
         <v>0</v>
       </c>
       <c r="I237" t="n">
-        <v>3232566.436897081</v>
+        <v>2084217.898556078</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>31517.93294318765</v>
+        <v>20321.38897932088</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>0</v>
       </c>
       <c r="N237" t="n">
-        <v>3232566.436897081</v>
+        <v>2084217.898556078</v>
       </c>
     </row>
     <row r="238">
@@ -10954,13 +10954,13 @@
         <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>3232566.436897081</v>
+        <v>2084217.898556078</v>
       </c>
       <c r="J238" t="n">
-        <v>2263.119762471411</v>
+        <v>1459.160950778984</v>
       </c>
       <c r="K238" t="n">
-        <v>33781.05270565907</v>
+        <v>21780.54993009986</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>3234829.556659553</v>
+        <v>2085677.059506857</v>
       </c>
     </row>
     <row r="239">
@@ -10998,13 +10998,13 @@
         <v>0</v>
       </c>
       <c r="I239" t="n">
-        <v>3234829.556659553</v>
+        <v>2085677.059506857</v>
       </c>
       <c r="J239" t="n">
-        <v>2264.70417261729</v>
+        <v>1460.182509360602</v>
       </c>
       <c r="K239" t="n">
-        <v>36045.75687827636</v>
+        <v>23240.73243946047</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -11013,7 +11013,7 @@
         <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>3237094.26083217</v>
+        <v>2087137.242016217</v>
       </c>
     </row>
     <row r="240">
@@ -11042,13 +11042,13 @@
         <v>0</v>
       </c>
       <c r="I240" t="n">
-        <v>3237094.26083217</v>
+        <v>2087137.242016217</v>
       </c>
       <c r="J240" t="n">
-        <v>2266.289692008402</v>
+        <v>1461.204783135559</v>
       </c>
       <c r="K240" t="n">
-        <v>38312.04657028476</v>
+        <v>24701.93722259603</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -11057,7 +11057,7 @@
         <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>3239360.550524178</v>
+        <v>2088598.446799353</v>
       </c>
     </row>
     <row r="241">
@@ -11086,13 +11086,13 @@
         <v>0</v>
       </c>
       <c r="I241" t="n">
-        <v>3239360.550524178</v>
+        <v>2088598.446799353</v>
       </c>
       <c r="J241" t="n">
-        <v>2267.876321421936</v>
+        <v>1462.227772604208</v>
       </c>
       <c r="K241" t="n">
-        <v>40579.92289170669</v>
+        <v>26164.16499520023</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -11101,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>3241628.4268456</v>
+        <v>2090060.674571957</v>
       </c>
     </row>
     <row r="242">
@@ -11130,13 +11130,13 @@
         <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>3241628.4268456</v>
+        <v>2090060.674571957</v>
       </c>
       <c r="J242" t="n">
-        <v>2269.464061634615</v>
+        <v>1463.251478267834</v>
       </c>
       <c r="K242" t="n">
-        <v>42849.38695334131</v>
+        <v>27627.41647346807</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -11145,7 +11145,7 @@
         <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>3243897.890907235</v>
+        <v>2091523.926050225</v>
       </c>
     </row>
     <row r="243">
@@ -11174,13 +11174,13 @@
         <v>0</v>
       </c>
       <c r="I243" t="n">
-        <v>3243897.890907235</v>
+        <v>2091523.926050225</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
       </c>
       <c r="K243" t="n">
-        <v>42849.38695334131</v>
+        <v>27627.41647346807</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
         <v>0</v>
       </c>
       <c r="N243" t="n">
-        <v>3243897.890907235</v>
+        <v>2091523.926050225</v>
       </c>
     </row>
     <row r="244">
@@ -11218,13 +11218,13 @@
         <v>0</v>
       </c>
       <c r="I244" t="n">
-        <v>3243897.890907235</v>
+        <v>2091523.926050225</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
       </c>
       <c r="K244" t="n">
-        <v>42849.38695334131</v>
+        <v>27627.41647346807</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>3243897.890907235</v>
+        <v>2091523.926050225</v>
       </c>
     </row>
     <row r="245">
@@ -11262,22 +11262,22 @@
         <v>1</v>
       </c>
       <c r="I245" t="n">
-        <v>3243897.890907235</v>
+        <v>2091523.926050225</v>
       </c>
       <c r="J245" t="n">
-        <v>2271.052913424093</v>
+        <v>1464.275900627719</v>
       </c>
       <c r="K245" t="n">
-        <v>45120.4398667654</v>
+        <v>29091.69237409579</v>
       </c>
       <c r="L245" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M245" t="n">
-        <v>-30120.4398667654</v>
+        <v>120908.3076259042</v>
       </c>
       <c r="N245" t="n">
-        <v>3231168.943820659</v>
+        <v>1942988.201950853</v>
       </c>
     </row>
     <row r="246">
@@ -11306,13 +11306,13 @@
         <v>0</v>
       </c>
       <c r="I246" t="n">
-        <v>3231168.943820659</v>
+        <v>1942988.201950853</v>
       </c>
       <c r="J246" t="n">
-        <v>2262.141377568711</v>
+        <v>1360.286040185718</v>
       </c>
       <c r="K246" t="n">
-        <v>2262.141377568711</v>
+        <v>1360.286040185718</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -11321,7 +11321,7 @@
         <v>0</v>
       </c>
       <c r="N246" t="n">
-        <v>3233431.085198228</v>
+        <v>1944348.487991038</v>
       </c>
     </row>
     <row r="247">
@@ -11350,13 +11350,13 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>3233431.085198228</v>
+        <v>1944348.487991038</v>
       </c>
       <c r="J247" t="n">
-        <v>2263.725102747325</v>
+        <v>1361.238376442576</v>
       </c>
       <c r="K247" t="n">
-        <v>4525.866480316035</v>
+        <v>2721.524416628294</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -11365,7 +11365,7 @@
         <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>3235694.810300975</v>
+        <v>1945709.726367481</v>
       </c>
     </row>
     <row r="248">
@@ -11394,13 +11394,13 @@
         <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>3235694.810300975</v>
+        <v>1945709.726367481</v>
       </c>
       <c r="J248" t="n">
-        <v>2265.309936691541</v>
+        <v>1362.191379429772</v>
       </c>
       <c r="K248" t="n">
-        <v>6791.176417007577</v>
+        <v>4083.715796058066</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -11409,7 +11409,7 @@
         <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>3237960.120237667</v>
+        <v>1947071.917746911</v>
       </c>
     </row>
     <row r="249">
@@ -11438,13 +11438,13 @@
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>3237960.120237667</v>
+        <v>1947071.917746911</v>
       </c>
       <c r="J249" t="n">
-        <v>2266.895880178548</v>
+        <v>1363.145049614599</v>
       </c>
       <c r="K249" t="n">
-        <v>9058.072297186125</v>
+        <v>5446.860845672665</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -11453,7 +11453,7 @@
         <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>3240227.016117845</v>
+        <v>1948435.062796525</v>
       </c>
     </row>
     <row r="250">
@@ -11482,13 +11482,13 @@
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>3240227.016117845</v>
+        <v>1948435.062796525</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>9058.072297186125</v>
+        <v>5446.860845672665</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>3240227.016117845</v>
+        <v>1948435.062796525</v>
       </c>
     </row>
     <row r="251">
@@ -11526,13 +11526,13 @@
         <v>0</v>
       </c>
       <c r="I251" t="n">
-        <v>3240227.016117845</v>
+        <v>1948435.062796525</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
       </c>
       <c r="K251" t="n">
-        <v>9058.072297186125</v>
+        <v>5446.860845672665</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -11541,7 +11541,7 @@
         <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>3240227.016117845</v>
+        <v>1948435.062796525</v>
       </c>
     </row>
     <row r="252">
@@ -11570,13 +11570,13 @@
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>3240227.016117845</v>
+        <v>1948435.062796525</v>
       </c>
       <c r="J252" t="n">
-        <v>2268.482933984138</v>
+        <v>1364.099387463881</v>
       </c>
       <c r="K252" t="n">
-        <v>11326.55523117026</v>
+        <v>6810.960233136546</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -11585,7 +11585,7 @@
         <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>3242495.499051829</v>
+        <v>1949799.162183989</v>
       </c>
     </row>
     <row r="253">
@@ -11614,13 +11614,13 @@
         <v>0</v>
       </c>
       <c r="I253" t="n">
-        <v>3242495.499051829</v>
+        <v>1949799.162183989</v>
       </c>
       <c r="J253" t="n">
-        <v>2270.071098885965</v>
+        <v>1365.054393444909</v>
       </c>
       <c r="K253" t="n">
-        <v>13596.62633005623</v>
+        <v>8176.014626581455</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -11629,7 +11629,7 @@
         <v>0</v>
       </c>
       <c r="N253" t="n">
-        <v>3244765.570150715</v>
+        <v>1951164.216577434</v>
       </c>
     </row>
     <row r="254">
@@ -11658,13 +11658,13 @@
         <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>3244765.570150715</v>
+        <v>1951164.216577434</v>
       </c>
       <c r="J254" t="n">
-        <v>2271.660375662614</v>
+        <v>1366.010068025906</v>
       </c>
       <c r="K254" t="n">
-        <v>15868.28670571884</v>
+        <v>9542.02469460736</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -11673,7 +11673,7 @@
         <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>3247037.230526378</v>
+        <v>1952530.22664546</v>
       </c>
     </row>
     <row r="255">
@@ -11702,13 +11702,13 @@
         <v>0</v>
       </c>
       <c r="I255" t="n">
-        <v>3247037.230526378</v>
+        <v>1952530.22664546</v>
       </c>
       <c r="J255" t="n">
-        <v>2273.250765091274</v>
+        <v>1366.966411674395</v>
       </c>
       <c r="K255" t="n">
-        <v>18141.53747081012</v>
+        <v>10908.99110628176</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -11717,7 +11717,7 @@
         <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>3249310.481291469</v>
+        <v>1953897.193057135</v>
       </c>
     </row>
     <row r="256">
@@ -11746,13 +11746,13 @@
         <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>3249310.481291469</v>
+        <v>1953897.193057135</v>
       </c>
       <c r="J256" t="n">
-        <v>2274.842267951928</v>
+        <v>1367.923424859298</v>
       </c>
       <c r="K256" t="n">
-        <v>20416.37973876204</v>
+        <v>12276.91453114105</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -11761,7 +11761,7 @@
         <v>0</v>
       </c>
       <c r="N256" t="n">
-        <v>3251585.323559421</v>
+        <v>1955265.116481994</v>
       </c>
     </row>
     <row r="257">
@@ -11790,13 +11790,13 @@
         <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>3251585.323559421</v>
+        <v>1955265.116481994</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
       </c>
       <c r="K257" t="n">
-        <v>20416.37973876204</v>
+        <v>12276.91453114105</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -11805,7 +11805,7 @@
         <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>3251585.323559421</v>
+        <v>1955265.116481994</v>
       </c>
     </row>
     <row r="258">
@@ -11834,13 +11834,13 @@
         <v>0</v>
       </c>
       <c r="I258" t="n">
-        <v>3251585.323559421</v>
+        <v>1955265.116481994</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
       </c>
       <c r="K258" t="n">
-        <v>20416.37973876204</v>
+        <v>12276.91453114105</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -11849,7 +11849,7 @@
         <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>3251585.323559421</v>
+        <v>1955265.116481994</v>
       </c>
     </row>
     <row r="259">
@@ -11878,13 +11878,13 @@
         <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>3251585.323559421</v>
+        <v>1955265.116481994</v>
       </c>
       <c r="J259" t="n">
-        <v>2276.434885024093</v>
+        <v>1368.88110804907</v>
       </c>
       <c r="K259" t="n">
-        <v>22692.81462378614</v>
+        <v>13645.79563919012</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -11893,7 +11893,7 @@
         <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>3253861.758444445</v>
+        <v>1956633.997590043</v>
       </c>
     </row>
     <row r="260">
@@ -11922,13 +11922,13 @@
         <v>0</v>
       </c>
       <c r="I260" t="n">
-        <v>3253861.758444445</v>
+        <v>1956633.997590043</v>
       </c>
       <c r="J260" t="n">
-        <v>2278.02861708682</v>
+        <v>1369.839461712865</v>
       </c>
       <c r="K260" t="n">
-        <v>24970.84324087296</v>
+        <v>15015.63510090299</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
@@ -11937,7 +11937,7 @@
         <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>3256139.787061532</v>
+        <v>1958003.837051756</v>
       </c>
     </row>
     <row r="261">
@@ -11966,13 +11966,13 @@
         <v>0</v>
       </c>
       <c r="I261" t="n">
-        <v>3256139.787061532</v>
+        <v>1958003.837051756</v>
       </c>
       <c r="J261" t="n">
-        <v>2279.623464921489</v>
+        <v>1370.798486319836</v>
       </c>
       <c r="K261" t="n">
-        <v>27250.46670579445</v>
+        <v>16386.43358722283</v>
       </c>
       <c r="L261" t="n">
         <v>0</v>
@@ -11981,7 +11981,7 @@
         <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>3258419.410526454</v>
+        <v>1959374.635538076</v>
       </c>
     </row>
     <row r="262">
@@ -12010,13 +12010,13 @@
         <v>0</v>
       </c>
       <c r="I262" t="n">
-        <v>3258419.410526454</v>
+        <v>1959374.635538076</v>
       </c>
       <c r="J262" t="n">
-        <v>2281.21942930948</v>
+        <v>1371.758182340069</v>
       </c>
       <c r="K262" t="n">
-        <v>29531.68613510393</v>
+        <v>17758.19176956289</v>
       </c>
       <c r="L262" t="n">
         <v>0</v>
@@ -12025,7 +12025,7 @@
         <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>3260700.629955763</v>
+        <v>1960746.393720416</v>
       </c>
     </row>
     <row r="263">
@@ -12054,13 +12054,13 @@
         <v>0</v>
       </c>
       <c r="I263" t="n">
-        <v>3260700.629955763</v>
+        <v>1960746.393720416</v>
       </c>
       <c r="J263" t="n">
-        <v>2282.816511032172</v>
+        <v>1372.718550243648</v>
       </c>
       <c r="K263" t="n">
-        <v>31814.5026461361</v>
+        <v>19130.91031980654</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -12069,7 +12069,7 @@
         <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>3262983.446466795</v>
+        <v>1962119.112270659</v>
       </c>
     </row>
     <row r="264">
@@ -12098,13 +12098,13 @@
         <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>3262983.446466795</v>
+        <v>1962119.112270659</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>31814.5026461361</v>
+        <v>19130.91031980654</v>
       </c>
       <c r="L264" t="n">
         <v>0</v>
@@ -12113,7 +12113,7 @@
         <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>3262983.446466795</v>
+        <v>1962119.112270659</v>
       </c>
     </row>
     <row r="265">
@@ -12142,13 +12142,13 @@
         <v>0</v>
       </c>
       <c r="I265" t="n">
-        <v>3262983.446466795</v>
+        <v>1962119.112270659</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
       </c>
       <c r="K265" t="n">
-        <v>31814.5026461361</v>
+        <v>19130.91031980654</v>
       </c>
       <c r="L265" t="n">
         <v>0</v>
@@ -12157,7 +12157,7 @@
         <v>0</v>
       </c>
       <c r="N265" t="n">
-        <v>3262983.446466795</v>
+        <v>1962119.112270659</v>
       </c>
     </row>
     <row r="266">
@@ -12186,13 +12186,13 @@
         <v>0</v>
       </c>
       <c r="I266" t="n">
-        <v>3262983.446466795</v>
+        <v>1962119.112270659</v>
       </c>
       <c r="J266" t="n">
-        <v>2284.41471087141</v>
+        <v>1373.679590500658</v>
       </c>
       <c r="K266" t="n">
-        <v>34098.91735700751</v>
+        <v>20504.5899103072</v>
       </c>
       <c r="L266" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>3265267.861177667</v>
+        <v>1963492.79186116</v>
       </c>
     </row>
     <row r="267">
@@ -12230,13 +12230,13 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>3265267.861177667</v>
+        <v>1963492.79186116</v>
       </c>
       <c r="J267" t="n">
-        <v>2286.014029610436</v>
+        <v>1374.641303581884</v>
       </c>
       <c r="K267" t="n">
-        <v>36384.93138661794</v>
+        <v>21879.23121388908</v>
       </c>
       <c r="L267" t="n">
         <v>0</v>
@@ -12245,7 +12245,7 @@
         <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>3267553.875207277</v>
+        <v>1964867.433164742</v>
       </c>
     </row>
     <row r="268">
@@ -12274,13 +12274,13 @@
         <v>0</v>
       </c>
       <c r="I268" t="n">
-        <v>3267553.875207277</v>
+        <v>1964867.433164742</v>
       </c>
       <c r="J268" t="n">
-        <v>2287.614468032494</v>
+        <v>1375.603689958574</v>
       </c>
       <c r="K268" t="n">
-        <v>38672.54585465044</v>
+        <v>23254.83490384766</v>
       </c>
       <c r="L268" t="n">
         <v>0</v>
@@ -12289,7 +12289,7 @@
         <v>0</v>
       </c>
       <c r="N268" t="n">
-        <v>3269841.48967531</v>
+        <v>1966243.0368547</v>
       </c>
     </row>
     <row r="269">
@@ -12318,13 +12318,13 @@
         <v>0</v>
       </c>
       <c r="I269" t="n">
-        <v>3269841.48967531</v>
+        <v>1966243.0368547</v>
       </c>
       <c r="J269" t="n">
-        <v>2289.216026921757</v>
+        <v>1376.566750101978</v>
       </c>
       <c r="K269" t="n">
-        <v>40961.76188157219</v>
+        <v>24631.40165394964</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -12333,7 +12333,7 @@
         <v>0</v>
       </c>
       <c r="N269" t="n">
-        <v>3272130.705702231</v>
+        <v>1967619.603604802</v>
       </c>
     </row>
     <row r="270">
@@ -12362,13 +12362,13 @@
         <v>0</v>
       </c>
       <c r="I270" t="n">
-        <v>3272130.705702231</v>
+        <v>1967619.603604802</v>
       </c>
       <c r="J270" t="n">
-        <v>2290.818707061931</v>
+        <v>1377.530484483577</v>
       </c>
       <c r="K270" t="n">
-        <v>43252.58058863413</v>
+        <v>26008.93213843321</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -12377,7 +12377,7 @@
         <v>0</v>
       </c>
       <c r="N270" t="n">
-        <v>3274421.524409293</v>
+        <v>1968997.134089286</v>
       </c>
     </row>
     <row r="271">
@@ -12406,13 +12406,13 @@
         <v>0</v>
       </c>
       <c r="I271" t="n">
-        <v>3274421.524409293</v>
+        <v>1968997.134089286</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
       </c>
       <c r="K271" t="n">
-        <v>43252.58058863413</v>
+        <v>26008.93213843321</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -12421,7 +12421,7 @@
         <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>3274421.524409293</v>
+        <v>1968997.134089286</v>
       </c>
     </row>
     <row r="272">
@@ -12450,13 +12450,13 @@
         <v>0</v>
       </c>
       <c r="I272" t="n">
-        <v>3274421.524409293</v>
+        <v>1968997.134089286</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>43252.58058863413</v>
+        <v>26008.93213843321</v>
       </c>
       <c r="L272" t="n">
         <v>0</v>
@@ -12465,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="N272" t="n">
-        <v>3274421.524409293</v>
+        <v>1968997.134089286</v>
       </c>
     </row>
     <row r="273">
@@ -12494,13 +12494,13 @@
         <v>0</v>
       </c>
       <c r="I273" t="n">
-        <v>3274421.524409293</v>
+        <v>1968997.134089286</v>
       </c>
       <c r="J273" t="n">
-        <v>2292.422509239055</v>
+        <v>1378.494893575786</v>
       </c>
       <c r="K273" t="n">
-        <v>45545.00309787318</v>
+        <v>27387.427032009</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -12509,7 +12509,7 @@
         <v>0</v>
       </c>
       <c r="N273" t="n">
-        <v>3276713.946918532</v>
+        <v>1970375.628982862</v>
       </c>
     </row>
     <row r="274">
@@ -12538,13 +12538,13 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>3276713.946918532</v>
+        <v>1970375.628982862</v>
       </c>
       <c r="J274" t="n">
-        <v>2294.027434237767</v>
+        <v>1379.459977850784</v>
       </c>
       <c r="K274" t="n">
-        <v>47839.03053211095</v>
+        <v>28766.88700985978</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -12553,7 +12553,7 @@
         <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>3279007.97435277</v>
+        <v>1971755.088960713</v>
       </c>
     </row>
     <row r="275">
@@ -12582,22 +12582,22 @@
         <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>3279007.97435277</v>
+        <v>1971755.088960713</v>
       </c>
       <c r="J275" t="n">
-        <v>2295.633482844103</v>
+        <v>1380.42573778145</v>
       </c>
       <c r="K275" t="n">
-        <v>50134.66401495505</v>
+        <v>30147.31274764123</v>
       </c>
       <c r="L275" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M275" t="n">
-        <v>-35134.66401495505</v>
+        <v>119852.6872523588</v>
       </c>
       <c r="N275" t="n">
-        <v>3266303.607835614</v>
+        <v>1823135.514698494</v>
       </c>
     </row>
     <row r="276">
@@ -12626,13 +12626,13 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>3266303.607835614</v>
+        <v>1823135.514698494</v>
       </c>
       <c r="J276" t="n">
-        <v>2286.739155845717</v>
+        <v>1276.377173840301</v>
       </c>
       <c r="K276" t="n">
-        <v>2286.739155845717</v>
+        <v>1276.377173840301</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -12641,7 +12641,7 @@
         <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>3268590.34699146</v>
+        <v>1824411.891872334</v>
       </c>
     </row>
     <row r="277">
@@ -12670,13 +12670,13 @@
         <v>0</v>
       </c>
       <c r="I277" t="n">
-        <v>3268590.34699146</v>
+        <v>1824411.891872334</v>
       </c>
       <c r="J277" t="n">
-        <v>2288.34010192845</v>
+        <v>1277.270765499678</v>
       </c>
       <c r="K277" t="n">
-        <v>4575.079257774167</v>
+        <v>2553.647939339979</v>
       </c>
       <c r="L277" t="n">
         <v>0</v>
@@ -12685,7 +12685,7 @@
         <v>0</v>
       </c>
       <c r="N277" t="n">
-        <v>3270878.687093388</v>
+        <v>1825689.162637834</v>
       </c>
     </row>
     <row r="278">
@@ -12714,13 +12714,13 @@
         <v>0</v>
       </c>
       <c r="I278" t="n">
-        <v>3270878.687093388</v>
+        <v>1825689.162637834</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>4575.079257774167</v>
+        <v>2553.647939339979</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>3270878.687093388</v>
+        <v>1825689.162637834</v>
       </c>
     </row>
     <row r="279">
@@ -12758,13 +12758,13 @@
         <v>0</v>
       </c>
       <c r="I279" t="n">
-        <v>3270878.687093388</v>
+        <v>1825689.162637834</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>4575.079257774167</v>
+        <v>2553.647939339979</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>0</v>
       </c>
       <c r="N279" t="n">
-        <v>3270878.687093388</v>
+        <v>1825689.162637834</v>
       </c>
     </row>
     <row r="280">
@@ -12802,13 +12802,13 @@
         <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>3270878.687093388</v>
+        <v>1825689.162637834</v>
       </c>
       <c r="J280" t="n">
-        <v>2289.942168834154</v>
+        <v>1278.164982762653</v>
       </c>
       <c r="K280" t="n">
-        <v>6865.02142660832</v>
+        <v>3831.812922102632</v>
       </c>
       <c r="L280" t="n">
         <v>0</v>
@@ -12817,7 +12817,7 @@
         <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>3273168.629262222</v>
+        <v>1826967.327620597</v>
       </c>
     </row>
     <row r="281">
@@ -12846,13 +12846,13 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>3273168.629262222</v>
+        <v>1826967.327620597</v>
       </c>
       <c r="J281" t="n">
-        <v>2291.545357346535</v>
+        <v>1279.059826067183</v>
       </c>
       <c r="K281" t="n">
-        <v>9156.566783954855</v>
+        <v>5110.872748169815</v>
       </c>
       <c r="L281" t="n">
         <v>0</v>
@@ -12861,7 +12861,7 @@
         <v>0</v>
       </c>
       <c r="N281" t="n">
-        <v>3275460.174619569</v>
+        <v>1828246.387446664</v>
       </c>
     </row>
     <row r="282">
@@ -12890,13 +12890,13 @@
         <v>0</v>
       </c>
       <c r="I282" t="n">
-        <v>3275460.174619569</v>
+        <v>1828246.387446664</v>
       </c>
       <c r="J282" t="n">
-        <v>2293.149668251164</v>
+        <v>1279.955295851454</v>
       </c>
       <c r="K282" t="n">
-        <v>11449.71645220602</v>
+        <v>6390.828044021269</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -12905,7 +12905,7 @@
         <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>3277753.32428782</v>
+        <v>1829526.342742515</v>
       </c>
     </row>
     <row r="283">
@@ -12934,13 +12934,13 @@
         <v>0</v>
       </c>
       <c r="I283" t="n">
-        <v>3277753.32428782</v>
+        <v>1829526.342742515</v>
       </c>
       <c r="J283" t="n">
-        <v>2294.755102333613</v>
+        <v>1280.851392553886</v>
       </c>
       <c r="K283" t="n">
-        <v>13744.47155453963</v>
+        <v>7671.679436575156</v>
       </c>
       <c r="L283" t="n">
         <v>0</v>
@@ -12949,7 +12949,7 @@
         <v>0</v>
       </c>
       <c r="N283" t="n">
-        <v>3280048.079390154</v>
+        <v>1830807.194135069</v>
       </c>
     </row>
     <row r="284">
@@ -12978,13 +12978,13 @@
         <v>0</v>
       </c>
       <c r="I284" t="n">
-        <v>3280048.079390154</v>
+        <v>1830807.194135069</v>
       </c>
       <c r="J284" t="n">
-        <v>2296.361660380848</v>
+        <v>1281.748116613831</v>
       </c>
       <c r="K284" t="n">
-        <v>16040.83321492048</v>
+        <v>8953.427553188987</v>
       </c>
       <c r="L284" t="n">
         <v>0</v>
@@ -12993,7 +12993,7 @@
         <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>3282344.441050535</v>
+        <v>1832088.942251683</v>
       </c>
     </row>
     <row r="285">
@@ -13022,13 +13022,13 @@
         <v>0</v>
       </c>
       <c r="I285" t="n">
-        <v>3282344.441050535</v>
+        <v>1832088.942251683</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
       </c>
       <c r="K285" t="n">
-        <v>16040.83321492048</v>
+        <v>8953.427553188987</v>
       </c>
       <c r="L285" t="n">
         <v>0</v>
@@ -13037,7 +13037,7 @@
         <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>3282344.441050535</v>
+        <v>1832088.942251683</v>
       </c>
     </row>
     <row r="286">
@@ -13066,13 +13066,13 @@
         <v>0</v>
       </c>
       <c r="I286" t="n">
-        <v>3282344.441050535</v>
+        <v>1832088.942251683</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
       </c>
       <c r="K286" t="n">
-        <v>16040.83321492048</v>
+        <v>8953.427553188987</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -13081,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>3282344.441050535</v>
+        <v>1832088.942251683</v>
       </c>
     </row>
     <row r="287">
@@ -13110,13 +13110,13 @@
         <v>0</v>
       </c>
       <c r="I287" t="n">
-        <v>3282344.441050535</v>
+        <v>1832088.942251683</v>
       </c>
       <c r="J287" t="n">
-        <v>2297.969343179371</v>
+        <v>1282.645468470408</v>
       </c>
       <c r="K287" t="n">
-        <v>18338.80255809985</v>
+        <v>10236.07302165939</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -13125,7 +13125,7 @@
         <v>0</v>
       </c>
       <c r="N287" t="n">
-        <v>3284642.410393714</v>
+        <v>1833371.587720153</v>
       </c>
     </row>
     <row r="288">
@@ -13154,13 +13154,13 @@
         <v>0</v>
       </c>
       <c r="I288" t="n">
-        <v>3284642.410393714</v>
+        <v>1833371.587720153</v>
       </c>
       <c r="J288" t="n">
-        <v>2299.578151516616</v>
+        <v>1283.543448562734</v>
       </c>
       <c r="K288" t="n">
-        <v>20638.38070961647</v>
+        <v>11519.61647022213</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
@@ -13169,7 +13169,7 @@
         <v>0</v>
       </c>
       <c r="N288" t="n">
-        <v>3286941.988545231</v>
+        <v>1834655.131168716</v>
       </c>
     </row>
     <row r="289">
@@ -13198,13 +13198,13 @@
         <v>0</v>
       </c>
       <c r="I289" t="n">
-        <v>3286941.988545231</v>
+        <v>1834655.131168716</v>
       </c>
       <c r="J289" t="n">
-        <v>2301.188086180482</v>
+        <v>1284.442057331093</v>
       </c>
       <c r="K289" t="n">
-        <v>22939.56879579695</v>
+        <v>12804.05852755322</v>
       </c>
       <c r="L289" t="n">
         <v>0</v>
@@ -13213,7 +13213,7 @@
         <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>3289243.176631411</v>
+        <v>1835939.573226047</v>
       </c>
     </row>
     <row r="290">
@@ -13242,13 +13242,13 @@
         <v>0</v>
       </c>
       <c r="I290" t="n">
-        <v>3289243.176631411</v>
+        <v>1835939.573226047</v>
       </c>
       <c r="J290" t="n">
-        <v>2302.799147959799</v>
+        <v>1285.341295215534</v>
       </c>
       <c r="K290" t="n">
-        <v>25242.36794375675</v>
+        <v>14089.39982276876</v>
       </c>
       <c r="L290" t="n">
         <v>0</v>
@@ -13257,7 +13257,7 @@
         <v>0</v>
       </c>
       <c r="N290" t="n">
-        <v>3291545.975779371</v>
+        <v>1837224.914521263</v>
       </c>
     </row>
     <row r="291">
@@ -13286,13 +13286,13 @@
         <v>0</v>
       </c>
       <c r="I291" t="n">
-        <v>3291545.975779371</v>
+        <v>1837224.914521263</v>
       </c>
       <c r="J291" t="n">
-        <v>2304.41133764293</v>
+        <v>1286.241162656341</v>
       </c>
       <c r="K291" t="n">
-        <v>27546.77928139968</v>
+        <v>15375.6409854251</v>
       </c>
       <c r="L291" t="n">
         <v>0</v>
@@ -13301,7 +13301,7 @@
         <v>0</v>
       </c>
       <c r="N291" t="n">
-        <v>3293850.387117014</v>
+        <v>1838511.155683919</v>
       </c>
     </row>
     <row r="292">
@@ -13330,13 +13330,13 @@
         <v>0</v>
       </c>
       <c r="I292" t="n">
-        <v>3293850.387117014</v>
+        <v>1838511.155683919</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
       </c>
       <c r="K292" t="n">
-        <v>27546.77928139968</v>
+        <v>15375.6409854251</v>
       </c>
       <c r="L292" t="n">
         <v>0</v>
@@ -13345,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="N292" t="n">
-        <v>3293850.387117014</v>
+        <v>1838511.155683919</v>
       </c>
     </row>
     <row r="293">
@@ -13374,13 +13374,13 @@
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>3293850.387117014</v>
+        <v>1838511.155683919</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
       </c>
       <c r="K293" t="n">
-        <v>27546.77928139968</v>
+        <v>15375.6409854251</v>
       </c>
       <c r="L293" t="n">
         <v>0</v>
@@ -13389,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="N293" t="n">
-        <v>3293850.387117014</v>
+        <v>1838511.155683919</v>
       </c>
     </row>
     <row r="294">
@@ -13418,13 +13418,13 @@
         <v>0</v>
       </c>
       <c r="I294" t="n">
-        <v>3293850.387117014</v>
+        <v>1838511.155683919</v>
       </c>
       <c r="J294" t="n">
-        <v>2306.024656020571</v>
+        <v>1287.141660094261</v>
       </c>
       <c r="K294" t="n">
-        <v>29852.80393742025</v>
+        <v>16662.78264551936</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -13433,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="N294" t="n">
-        <v>3296156.411773034</v>
+        <v>1839798.297344013</v>
       </c>
     </row>
     <row r="295">
@@ -13462,13 +13462,13 @@
         <v>0</v>
       </c>
       <c r="I295" t="n">
-        <v>3296156.411773034</v>
+        <v>1839798.297344013</v>
       </c>
       <c r="J295" t="n">
-        <v>2307.639103882015</v>
+        <v>1288.042787970509</v>
       </c>
       <c r="K295" t="n">
-        <v>32160.44304130226</v>
+        <v>17950.82543348987</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>3298464.050876916</v>
+        <v>1841086.340131984</v>
       </c>
     </row>
     <row r="296">
@@ -13506,13 +13506,13 @@
         <v>0</v>
       </c>
       <c r="I296" t="n">
-        <v>3298464.050876916</v>
+        <v>1841086.340131984</v>
       </c>
       <c r="J296" t="n">
-        <v>2309.254682018887</v>
+        <v>1288.944546726299</v>
       </c>
       <c r="K296" t="n">
-        <v>34469.69772332115</v>
+        <v>19239.76998021617</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
@@ -13521,7 +13521,7 @@
         <v>0</v>
       </c>
       <c r="N296" t="n">
-        <v>3300773.305558935</v>
+        <v>1842375.28467871</v>
       </c>
     </row>
     <row r="297">
@@ -13550,13 +13550,13 @@
         <v>0</v>
       </c>
       <c r="I297" t="n">
-        <v>3300773.305558935</v>
+        <v>1842375.28467871</v>
       </c>
       <c r="J297" t="n">
-        <v>2310.871391221881</v>
+        <v>1289.846936803544</v>
       </c>
       <c r="K297" t="n">
-        <v>36780.56911454303</v>
+        <v>20529.61691701971</v>
       </c>
       <c r="L297" t="n">
         <v>0</v>
@@ -13565,7 +13565,7 @@
         <v>0</v>
       </c>
       <c r="N297" t="n">
-        <v>3303084.176950157</v>
+        <v>1843665.131615514</v>
       </c>
     </row>
     <row r="298">
@@ -13594,13 +13594,13 @@
         <v>0</v>
       </c>
       <c r="I298" t="n">
-        <v>3303084.176950157</v>
+        <v>1843665.131615514</v>
       </c>
       <c r="J298" t="n">
-        <v>2312.48923228262</v>
+        <v>1290.749958643923</v>
       </c>
       <c r="K298" t="n">
-        <v>39093.05834682565</v>
+        <v>21820.36687566363</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -13609,7 +13609,7 @@
         <v>0</v>
       </c>
       <c r="N298" t="n">
-        <v>3305396.66618244</v>
+        <v>1844955.881574158</v>
       </c>
     </row>
     <row r="299">
@@ -13638,13 +13638,13 @@
         <v>0</v>
       </c>
       <c r="I299" t="n">
-        <v>3305396.66618244</v>
+        <v>1844955.881574158</v>
       </c>
       <c r="J299" t="n">
         <v>0</v>
       </c>
       <c r="K299" t="n">
-        <v>39093.05834682565</v>
+        <v>21820.36687566363</v>
       </c>
       <c r="L299" t="n">
         <v>0</v>
@@ -13653,7 +13653,7 @@
         <v>0</v>
       </c>
       <c r="N299" t="n">
-        <v>3305396.66618244</v>
+        <v>1844955.881574158</v>
       </c>
     </row>
     <row r="300">
@@ -13682,13 +13682,13 @@
         <v>0</v>
       </c>
       <c r="I300" t="n">
-        <v>3305396.66618244</v>
+        <v>1844955.881574158</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>39093.05834682565</v>
+        <v>21820.36687566363</v>
       </c>
       <c r="L300" t="n">
         <v>0</v>
@@ -13697,7 +13697,7 @@
         <v>0</v>
       </c>
       <c r="N300" t="n">
-        <v>3305396.66618244</v>
+        <v>1844955.881574158</v>
       </c>
     </row>
     <row r="301">
@@ -13726,13 +13726,13 @@
         <v>0</v>
       </c>
       <c r="I301" t="n">
-        <v>3305396.66618244</v>
+        <v>1844955.881574158</v>
       </c>
       <c r="J301" t="n">
-        <v>2314.108205994125</v>
+        <v>1291.653612690046</v>
       </c>
       <c r="K301" t="n">
-        <v>41407.16655281978</v>
+        <v>23112.02048835368</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>3307710.774388434</v>
+        <v>1846247.535186848</v>
       </c>
     </row>
     <row r="302">
@@ -13770,13 +13770,13 @@
         <v>0</v>
       </c>
       <c r="I302" t="n">
-        <v>3307710.774388434</v>
+        <v>1846247.535186848</v>
       </c>
       <c r="J302" t="n">
-        <v>2315.728313149419</v>
+        <v>1292.557899384294</v>
       </c>
       <c r="K302" t="n">
-        <v>43722.8948659692</v>
+        <v>24404.57838773797</v>
       </c>
       <c r="L302" t="n">
         <v>0</v>
@@ -13785,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="N302" t="n">
-        <v>3310026.502701583</v>
+        <v>1847540.093086232</v>
       </c>
     </row>
     <row r="303">
@@ -13814,13 +13814,13 @@
         <v>0</v>
       </c>
       <c r="I303" t="n">
-        <v>3310026.502701583</v>
+        <v>1847540.093086232</v>
       </c>
       <c r="J303" t="n">
-        <v>2317.349554541521</v>
+        <v>1293.462819169741</v>
       </c>
       <c r="K303" t="n">
-        <v>46040.24442051072</v>
+        <v>25698.04120690771</v>
       </c>
       <c r="L303" t="n">
         <v>0</v>
@@ -13829,7 +13829,7 @@
         <v>0</v>
       </c>
       <c r="N303" t="n">
-        <v>3312343.852256125</v>
+        <v>1848833.555905402</v>
       </c>
     </row>
     <row r="304">
@@ -13858,13 +13858,13 @@
         <v>0</v>
       </c>
       <c r="I304" t="n">
-        <v>3312343.852256125</v>
+        <v>1848833.555905402</v>
       </c>
       <c r="J304" t="n">
-        <v>2318.971930964384</v>
+        <v>1294.368372489233</v>
       </c>
       <c r="K304" t="n">
-        <v>48359.2163514751</v>
+        <v>26992.40957939695</v>
       </c>
       <c r="L304" t="n">
         <v>0</v>
@@ -13873,7 +13873,7 @@
         <v>0</v>
       </c>
       <c r="N304" t="n">
-        <v>3314662.824187089</v>
+        <v>1850127.924277891</v>
       </c>
     </row>
     <row r="305">
@@ -13902,13 +13902,13 @@
         <v>0</v>
       </c>
       <c r="I305" t="n">
-        <v>3314662.824187089</v>
+        <v>1850127.924277891</v>
       </c>
       <c r="J305" t="n">
-        <v>2320.595443213359</v>
+        <v>1295.274559787009</v>
       </c>
       <c r="K305" t="n">
-        <v>50679.81179468846</v>
+        <v>28287.68413918396</v>
       </c>
       <c r="L305" t="n">
         <v>0</v>
@@ -13917,7 +13917,7 @@
         <v>0</v>
       </c>
       <c r="N305" t="n">
-        <v>3316983.419630303</v>
+        <v>1851423.198837678</v>
       </c>
     </row>
     <row r="306">
@@ -13946,13 +13946,13 @@
         <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>3316983.419630303</v>
+        <v>1851423.198837678</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>
       </c>
       <c r="K306" t="n">
-        <v>50679.81179468846</v>
+        <v>28287.68413918396</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -13961,7 +13961,7 @@
         <v>0</v>
       </c>
       <c r="N306" t="n">
-        <v>3316983.419630303</v>
+        <v>1851423.198837678</v>
       </c>
     </row>
     <row r="307">
@@ -13990,13 +13990,13 @@
         <v>0</v>
       </c>
       <c r="I307" t="n">
-        <v>3316983.419630303</v>
+        <v>1851423.198837678</v>
       </c>
       <c r="J307" t="n">
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>50679.81179468846</v>
+        <v>28287.68413918396</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -14005,7 +14005,7 @@
         <v>0</v>
       </c>
       <c r="N307" t="n">
-        <v>3316983.419630303</v>
+        <v>1851423.198837678</v>
       </c>
     </row>
     <row r="308">
@@ -14034,22 +14034,22 @@
         <v>1</v>
       </c>
       <c r="I308" t="n">
-        <v>3316983.419630303</v>
+        <v>1851423.198837678</v>
       </c>
       <c r="J308" t="n">
-        <v>2322.220092083327</v>
+        <v>1296.181381506147</v>
       </c>
       <c r="K308" t="n">
-        <v>53002.03188677179</v>
+        <v>29583.8655206901</v>
       </c>
       <c r="L308" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M308" t="n">
-        <v>-38002.03188677179</v>
+        <v>120416.1344793099</v>
       </c>
       <c r="N308" t="n">
-        <v>3304305.639722386</v>
+        <v>1702719.380219184</v>
       </c>
     </row>
     <row r="309">
@@ -14078,13 +14078,13 @@
         <v>0</v>
       </c>
       <c r="I309" t="n">
-        <v>3304305.639722386</v>
+        <v>1702719.380219184</v>
       </c>
       <c r="J309" t="n">
-        <v>2313.344378369395</v>
+        <v>1192.073838091455</v>
       </c>
       <c r="K309" t="n">
-        <v>2313.344378369395</v>
+        <v>1192.073838091455</v>
       </c>
       <c r="L309" t="n">
         <v>0</v>
@@ -14093,7 +14093,7 @@
         <v>0</v>
       </c>
       <c r="N309" t="n">
-        <v>3306618.984100755</v>
+        <v>1703911.454057276</v>
       </c>
     </row>
     <row r="310">
@@ -14122,13 +14122,13 @@
         <v>0</v>
       </c>
       <c r="I310" t="n">
-        <v>3306618.984100755</v>
+        <v>1703911.454057276</v>
       </c>
       <c r="J310" t="n">
-        <v>2314.963950769044</v>
+        <v>1192.908408985473</v>
       </c>
       <c r="K310" t="n">
-        <v>4628.308329138439</v>
+        <v>2384.982247076929</v>
       </c>
       <c r="L310" t="n">
         <v>0</v>
@@ -14137,7 +14137,7 @@
         <v>0</v>
       </c>
       <c r="N310" t="n">
-        <v>3308933.948051524</v>
+        <v>1705104.362466261</v>
       </c>
     </row>
     <row r="311">
@@ -14166,13 +14166,13 @@
         <v>0</v>
       </c>
       <c r="I311" t="n">
-        <v>3308933.948051524</v>
+        <v>1705104.362466261</v>
       </c>
       <c r="J311" t="n">
-        <v>2316.584657030646</v>
+        <v>1193.743564162636</v>
       </c>
       <c r="K311" t="n">
-        <v>6944.892986169085</v>
+        <v>3578.725811239565</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -14181,7 +14181,7 @@
         <v>0</v>
       </c>
       <c r="N311" t="n">
-        <v>3311250.532708555</v>
+        <v>1706298.106030424</v>
       </c>
     </row>
     <row r="312">
@@ -14210,13 +14210,13 @@
         <v>0</v>
       </c>
       <c r="I312" t="n">
-        <v>3311250.532708555</v>
+        <v>1706298.106030424</v>
       </c>
       <c r="J312" t="n">
-        <v>2318.206497949082</v>
+        <v>1194.579304031795</v>
       </c>
       <c r="K312" t="n">
-        <v>9263.099484118167</v>
+        <v>4773.30511527136</v>
       </c>
       <c r="L312" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>0</v>
       </c>
       <c r="N312" t="n">
-        <v>3313568.739206504</v>
+        <v>1707492.685334455</v>
       </c>
     </row>
     <row r="313">
@@ -14254,13 +14254,13 @@
         <v>0</v>
       </c>
       <c r="I313" t="n">
-        <v>3313568.739206504</v>
+        <v>1707492.685334455</v>
       </c>
       <c r="J313" t="n">
         <v>0</v>
       </c>
       <c r="K313" t="n">
-        <v>9263.099484118167</v>
+        <v>4773.30511527136</v>
       </c>
       <c r="L313" t="n">
         <v>0</v>
@@ -14269,7 +14269,7 @@
         <v>0</v>
       </c>
       <c r="N313" t="n">
-        <v>3313568.739206504</v>
+        <v>1707492.685334455</v>
       </c>
     </row>
     <row r="314">
@@ -14298,13 +14298,13 @@
         <v>0</v>
       </c>
       <c r="I314" t="n">
-        <v>3313568.739206504</v>
+        <v>1707492.685334455</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>9263.099484118167</v>
+        <v>4773.30511527136</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -14313,7 +14313,7 @@
         <v>0</v>
       </c>
       <c r="N314" t="n">
-        <v>3313568.739206504</v>
+        <v>1707492.685334455</v>
       </c>
     </row>
     <row r="315">
@@ -14342,13 +14342,13 @@
         <v>0</v>
       </c>
       <c r="I315" t="n">
-        <v>3313568.739206504</v>
+        <v>1707492.685334455</v>
       </c>
       <c r="J315" t="n">
-        <v>2319.829474318307</v>
+        <v>1195.415629002731</v>
       </c>
       <c r="K315" t="n">
-        <v>11582.92895843647</v>
+        <v>5968.720744274091</v>
       </c>
       <c r="L315" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
         <v>0</v>
       </c>
       <c r="N315" t="n">
-        <v>3315888.568680822</v>
+        <v>1708688.100963458</v>
       </c>
     </row>
     <row r="316">
@@ -14386,13 +14386,13 @@
         <v>0</v>
       </c>
       <c r="I316" t="n">
-        <v>3315888.568680822</v>
+        <v>1708688.100963458</v>
       </c>
       <c r="J316" t="n">
-        <v>2321.453586933203</v>
+        <v>1196.252539484529</v>
       </c>
       <c r="K316" t="n">
-        <v>13904.38254536968</v>
+        <v>7164.97328375862</v>
       </c>
       <c r="L316" t="n">
         <v>0</v>
@@ -14401,7 +14401,7 @@
         <v>0</v>
       </c>
       <c r="N316" t="n">
-        <v>3318210.022267756</v>
+        <v>1709884.353502943</v>
       </c>
     </row>
     <row r="317">
@@ -14430,13 +14430,13 @@
         <v>0</v>
       </c>
       <c r="I317" t="n">
-        <v>3318210.022267756</v>
+        <v>1709884.353502943</v>
       </c>
       <c r="J317" t="n">
-        <v>2323.078836589586</v>
+        <v>1197.090035887435</v>
       </c>
       <c r="K317" t="n">
-        <v>16227.46138195926</v>
+        <v>8362.063319646055</v>
       </c>
       <c r="L317" t="n">
         <v>0</v>
@@ -14445,7 +14445,7 @@
         <v>0</v>
       </c>
       <c r="N317" t="n">
-        <v>3320533.101104345</v>
+        <v>1711081.44353883</v>
       </c>
     </row>
     <row r="318">
@@ -14474,13 +14474,13 @@
         <v>0</v>
       </c>
       <c r="I318" t="n">
-        <v>3320533.101104345</v>
+        <v>1711081.44353883</v>
       </c>
       <c r="J318" t="n">
-        <v>2324.705224083271</v>
+        <v>1197.928118621465</v>
       </c>
       <c r="K318" t="n">
-        <v>18552.16660604253</v>
+        <v>9559.99143826752</v>
       </c>
       <c r="L318" t="n">
         <v>0</v>
@@ -14489,7 +14489,7 @@
         <v>0</v>
       </c>
       <c r="N318" t="n">
-        <v>3322857.806328428</v>
+        <v>1712279.371657452</v>
       </c>
     </row>
     <row r="319">
@@ -14518,13 +14518,13 @@
         <v>0</v>
       </c>
       <c r="I319" t="n">
-        <v>3322857.806328428</v>
+        <v>1712279.371657452</v>
       </c>
       <c r="J319" t="n">
-        <v>2326.332750210539</v>
+        <v>1198.766788097331</v>
       </c>
       <c r="K319" t="n">
-        <v>20878.49935625307</v>
+        <v>10758.75822636485</v>
       </c>
       <c r="L319" t="n">
         <v>0</v>
@@ -14533,7 +14533,7 @@
         <v>0</v>
       </c>
       <c r="N319" t="n">
-        <v>3325184.139078639</v>
+        <v>1713478.138445549</v>
       </c>
     </row>
     <row r="320">
@@ -14562,13 +14562,13 @@
         <v>0</v>
       </c>
       <c r="I320" t="n">
-        <v>3325184.139078639</v>
+        <v>1713478.138445549</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
       </c>
       <c r="K320" t="n">
-        <v>20878.49935625307</v>
+        <v>10758.75822636485</v>
       </c>
       <c r="L320" t="n">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>0</v>
       </c>
       <c r="N320" t="n">
-        <v>3325184.139078639</v>
+        <v>1713478.138445549</v>
       </c>
     </row>
     <row r="321">
@@ -14610,13 +14610,13 @@
         <v>0</v>
       </c>
       <c r="I321" t="n">
-        <v>3325184.139078639</v>
+        <v>1713478.138445549</v>
       </c>
       <c r="J321" t="n">
         <v>0</v>
       </c>
       <c r="K321" t="n">
-        <v>20878.49935625307</v>
+        <v>10758.75822636485</v>
       </c>
       <c r="L321" t="n">
         <v>0</v>
@@ -14625,7 +14625,7 @@
         <v>0</v>
       </c>
       <c r="N321" t="n">
-        <v>3325184.139078639</v>
+        <v>1713478.138445549</v>
       </c>
     </row>
     <row r="322">
@@ -14654,13 +14654,13 @@
         <v>0</v>
       </c>
       <c r="I322" t="n">
-        <v>3325184.139078639</v>
+        <v>1713478.138445549</v>
       </c>
       <c r="J322" t="n">
-        <v>2327.961415769067</v>
+        <v>1199.606044725748</v>
       </c>
       <c r="K322" t="n">
-        <v>23206.46077202214</v>
+        <v>11958.3642710906</v>
       </c>
       <c r="L322" t="n">
         <v>0</v>
@@ -14669,7 +14669,7 @@
         <v>0</v>
       </c>
       <c r="N322" t="n">
-        <v>3327512.100494408</v>
+        <v>1714677.744490275</v>
       </c>
     </row>
     <row r="323">
@@ -14698,13 +14698,13 @@
         <v>0</v>
       </c>
       <c r="I323" t="n">
-        <v>3327512.100494408</v>
+        <v>1714677.744490275</v>
       </c>
       <c r="J323" t="n">
-        <v>2329.591221556067</v>
+        <v>1200.44588891766</v>
       </c>
       <c r="K323" t="n">
-        <v>25536.05199357821</v>
+        <v>13158.81016000826</v>
       </c>
       <c r="L323" t="n">
         <v>0</v>
@@ -14713,7 +14713,7 @@
         <v>0</v>
       </c>
       <c r="N323" t="n">
-        <v>3329841.691715964</v>
+        <v>1715878.190379192</v>
       </c>
     </row>
     <row r="324">
@@ -14742,13 +14742,13 @@
         <v>0</v>
       </c>
       <c r="I324" t="n">
-        <v>3329841.691715964</v>
+        <v>1715878.190379192</v>
       </c>
       <c r="J324" t="n">
-        <v>2331.22216837015</v>
+        <v>1201.286321084481</v>
       </c>
       <c r="K324" t="n">
-        <v>27867.27416194836</v>
+        <v>14360.09648109274</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>0</v>
       </c>
       <c r="N324" t="n">
-        <v>3332172.913884334</v>
+        <v>1717079.476700277</v>
       </c>
     </row>
     <row r="325">
@@ -14786,13 +14786,13 @@
         <v>0</v>
       </c>
       <c r="I325" t="n">
-        <v>3332172.913884334</v>
+        <v>1717079.476700277</v>
       </c>
       <c r="J325" t="n">
-        <v>2332.854257010389</v>
+        <v>1202.127341637854</v>
       </c>
       <c r="K325" t="n">
-        <v>30200.12841895875</v>
+        <v>15562.22382273059</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="N325" t="n">
-        <v>3334505.768141345</v>
+        <v>1718281.604041915</v>
       </c>
     </row>
     <row r="326">
@@ -14830,13 +14830,13 @@
         <v>0</v>
       </c>
       <c r="I326" t="n">
-        <v>3334505.768141345</v>
+        <v>1718281.604041915</v>
       </c>
       <c r="J326" t="n">
-        <v>2334.48748827586</v>
+        <v>1202.968950989656</v>
       </c>
       <c r="K326" t="n">
-        <v>32534.61590723461</v>
+        <v>16765.19277372025</v>
       </c>
       <c r="L326" t="n">
         <v>0</v>
@@ -14845,7 +14845,7 @@
         <v>0</v>
       </c>
       <c r="N326" t="n">
-        <v>3336840.255629621</v>
+        <v>1719484.572992904</v>
       </c>
     </row>
     <row r="327">
@@ -14874,13 +14874,13 @@
         <v>0</v>
       </c>
       <c r="I327" t="n">
-        <v>3336840.255629621</v>
+        <v>1719484.572992904</v>
       </c>
       <c r="J327" t="n">
         <v>0</v>
       </c>
       <c r="K327" t="n">
-        <v>32534.61590723461</v>
+        <v>16765.19277372025</v>
       </c>
       <c r="L327" t="n">
         <v>0</v>
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="N327" t="n">
-        <v>3336840.255629621</v>
+        <v>1719484.572992904</v>
       </c>
     </row>
     <row r="328">
@@ -14918,13 +14918,13 @@
         <v>0</v>
       </c>
       <c r="I328" t="n">
-        <v>3336840.255629621</v>
+        <v>1719484.572992904</v>
       </c>
       <c r="J328" t="n">
         <v>0</v>
       </c>
       <c r="K328" t="n">
-        <v>32534.61590723461</v>
+        <v>16765.19277372025</v>
       </c>
       <c r="L328" t="n">
         <v>0</v>
@@ -14933,7 +14933,7 @@
         <v>0</v>
       </c>
       <c r="N328" t="n">
-        <v>3336840.255629621</v>
+        <v>1719484.572992904</v>
       </c>
     </row>
     <row r="329">
@@ -14962,13 +14962,13 @@
         <v>0</v>
       </c>
       <c r="I329" t="n">
-        <v>3336840.255629621</v>
+        <v>1719484.572992904</v>
       </c>
       <c r="J329" t="n">
-        <v>2336.121862966102</v>
+        <v>1203.811149552232</v>
       </c>
       <c r="K329" t="n">
-        <v>34870.73777020071</v>
+        <v>17969.00392327248</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
@@ -14977,7 +14977,7 @@
         <v>0</v>
       </c>
       <c r="N329" t="n">
-        <v>3339176.377492587</v>
+        <v>1720688.384142457</v>
       </c>
     </row>
     <row r="330">
@@ -15006,13 +15006,13 @@
         <v>0</v>
       </c>
       <c r="I330" t="n">
-        <v>3339176.377492587</v>
+        <v>1720688.384142457</v>
       </c>
       <c r="J330" t="n">
-        <v>2337.757381882519</v>
+        <v>1204.653937738156</v>
       </c>
       <c r="K330" t="n">
-        <v>37208.49515208323</v>
+        <v>19173.65786101064</v>
       </c>
       <c r="L330" t="n">
         <v>0</v>
@@ -15021,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="N330" t="n">
-        <v>3341514.134874469</v>
+        <v>1721893.038080195</v>
       </c>
     </row>
     <row r="331">
@@ -15050,13 +15050,13 @@
         <v>0</v>
       </c>
       <c r="I331" t="n">
-        <v>3341514.134874469</v>
+        <v>1721893.038080195</v>
       </c>
       <c r="J331" t="n">
-        <v>2339.394045825582</v>
+        <v>1205.497315960005</v>
       </c>
       <c r="K331" t="n">
-        <v>39547.88919790881</v>
+        <v>20379.15517697064</v>
       </c>
       <c r="L331" t="n">
         <v>0</v>
@@ -15065,7 +15065,7 @@
         <v>0</v>
       </c>
       <c r="N331" t="n">
-        <v>3343853.528920295</v>
+        <v>1723098.535396155</v>
       </c>
     </row>
     <row r="332">
@@ -15094,13 +15094,13 @@
         <v>0</v>
       </c>
       <c r="I332" t="n">
-        <v>3343853.528920295</v>
+        <v>1723098.535396155</v>
       </c>
       <c r="J332" t="n">
-        <v>2341.031855597161</v>
+        <v>1206.34128463082</v>
       </c>
       <c r="K332" t="n">
-        <v>41888.92105350597</v>
+        <v>21585.49646160146</v>
       </c>
       <c r="L332" t="n">
         <v>0</v>
@@ -15109,7 +15109,7 @@
         <v>0</v>
       </c>
       <c r="N332" t="n">
-        <v>3346194.560775892</v>
+        <v>1724304.876680786</v>
       </c>
     </row>
     <row r="333">
@@ -15138,13 +15138,13 @@
         <v>0</v>
       </c>
       <c r="I333" t="n">
-        <v>3346194.560775892</v>
+        <v>1724304.876680786</v>
       </c>
       <c r="J333" t="n">
-        <v>2342.670811999124</v>
+        <v>1207.185844164109</v>
       </c>
       <c r="K333" t="n">
-        <v>44231.59186550509</v>
+        <v>22792.68230576557</v>
       </c>
       <c r="L333" t="n">
         <v>0</v>
@@ -15153,7 +15153,7 @@
         <v>0</v>
       </c>
       <c r="N333" t="n">
-        <v>3348537.231587891</v>
+        <v>1725512.06252495</v>
       </c>
     </row>
     <row r="334">
@@ -15182,13 +15182,13 @@
         <v>0</v>
       </c>
       <c r="I334" t="n">
-        <v>3348537.231587891</v>
+        <v>1725512.06252495</v>
       </c>
       <c r="J334" t="n">
         <v>0</v>
       </c>
       <c r="K334" t="n">
-        <v>44231.59186550509</v>
+        <v>22792.68230576557</v>
       </c>
       <c r="L334" t="n">
         <v>0</v>
@@ -15197,7 +15197,7 @@
         <v>0</v>
       </c>
       <c r="N334" t="n">
-        <v>3348537.231587891</v>
+        <v>1725512.06252495</v>
       </c>
     </row>
     <row r="335">
@@ -15226,13 +15226,13 @@
         <v>0</v>
       </c>
       <c r="I335" t="n">
-        <v>3348537.231587891</v>
+        <v>1725512.06252495</v>
       </c>
       <c r="J335" t="n">
         <v>0</v>
       </c>
       <c r="K335" t="n">
-        <v>44231.59186550509</v>
+        <v>22792.68230576557</v>
       </c>
       <c r="L335" t="n">
         <v>0</v>
@@ -15241,7 +15241,7 @@
         <v>0</v>
       </c>
       <c r="N335" t="n">
-        <v>3348537.231587891</v>
+        <v>1725512.06252495</v>
       </c>
     </row>
     <row r="336">
@@ -15270,13 +15270,13 @@
         <v>0</v>
       </c>
       <c r="I336" t="n">
-        <v>3348537.231587891</v>
+        <v>1725512.06252495</v>
       </c>
       <c r="J336" t="n">
-        <v>2344.310915834736</v>
+        <v>1208.030994973611</v>
       </c>
       <c r="K336" t="n">
-        <v>46575.90278133983</v>
+        <v>24000.71330073918</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -15285,7 +15285,7 @@
         <v>0</v>
       </c>
       <c r="N336" t="n">
-        <v>3350881.542503726</v>
+        <v>1726720.093519923</v>
       </c>
     </row>
     <row r="337">
@@ -15314,22 +15314,22 @@
         <v>1</v>
       </c>
       <c r="I337" t="n">
-        <v>3350881.542503726</v>
+        <v>1726720.093519923</v>
       </c>
       <c r="J337" t="n">
-        <v>2345.952167906798</v>
+        <v>1208.8767374733</v>
       </c>
       <c r="K337" t="n">
-        <v>48921.85494924663</v>
+        <v>25209.59003821248</v>
       </c>
       <c r="L337" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M337" t="n">
-        <v>-33921.85494924663</v>
+        <v>124790.4099617875</v>
       </c>
       <c r="N337" t="n">
-        <v>3338227.494671633</v>
+        <v>1577928.970257397</v>
       </c>
     </row>
     <row r="338">
@@ -15358,13 +15358,13 @@
         <v>0</v>
       </c>
       <c r="I338" t="n">
-        <v>3338227.494671633</v>
+        <v>1577928.970257397</v>
       </c>
       <c r="J338" t="n">
-        <v>2337.093069019727</v>
+        <v>1104.70807207725</v>
       </c>
       <c r="K338" t="n">
-        <v>2337.093069019727</v>
+        <v>1104.70807207725</v>
       </c>
       <c r="L338" t="n">
         <v>0</v>
@@ -15373,7 +15373,7 @@
         <v>0</v>
       </c>
       <c r="N338" t="n">
-        <v>3340564.587740652</v>
+        <v>1579033.678329474</v>
       </c>
     </row>
     <row r="339">
@@ -15402,13 +15402,13 @@
         <v>0</v>
       </c>
       <c r="I339" t="n">
-        <v>3340564.587740652</v>
+        <v>1579033.678329474</v>
       </c>
       <c r="J339" t="n">
-        <v>2338.729267877061</v>
+        <v>1105.481478198431</v>
       </c>
       <c r="K339" t="n">
-        <v>4675.822336896788</v>
+        <v>2210.189550275682</v>
       </c>
       <c r="L339" t="n">
         <v>0</v>
@@ -15417,7 +15417,7 @@
         <v>0</v>
       </c>
       <c r="N339" t="n">
-        <v>3342903.317008529</v>
+        <v>1580139.159807672</v>
       </c>
     </row>
     <row r="340">
@@ -15446,13 +15446,13 @@
         <v>0</v>
       </c>
       <c r="I340" t="n">
-        <v>3342903.317008529</v>
+        <v>1580139.159807672</v>
       </c>
       <c r="J340" t="n">
-        <v>2340.366612237412</v>
+        <v>1106.255425781244</v>
       </c>
       <c r="K340" t="n">
-        <v>7016.188949134201</v>
+        <v>3316.444976056926</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
@@ -15461,7 +15461,7 @@
         <v>0</v>
       </c>
       <c r="N340" t="n">
-        <v>3345243.683620767</v>
+        <v>1581245.415233454</v>
       </c>
     </row>
     <row r="341">
@@ -15490,13 +15490,13 @@
         <v>0</v>
       </c>
       <c r="I341" t="n">
-        <v>3345243.683620767</v>
+        <v>1581245.415233454</v>
       </c>
       <c r="J341" t="n">
         <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>7016.188949134201</v>
+        <v>3316.444976056926</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -15505,7 +15505,7 @@
         <v>0</v>
       </c>
       <c r="N341" t="n">
-        <v>3345243.683620767</v>
+        <v>1581245.415233454</v>
       </c>
     </row>
     <row r="342">
@@ -15534,13 +15534,13 @@
         <v>0</v>
       </c>
       <c r="I342" t="n">
-        <v>3345243.683620767</v>
+        <v>1581245.415233454</v>
       </c>
       <c r="J342" t="n">
         <v>0</v>
       </c>
       <c r="K342" t="n">
-        <v>7016.188949134201</v>
+        <v>3316.444976056926</v>
       </c>
       <c r="L342" t="n">
         <v>0</v>
@@ -15549,7 +15549,7 @@
         <v>0</v>
       </c>
       <c r="N342" t="n">
-        <v>3345243.683620767</v>
+        <v>1581245.415233454</v>
       </c>
     </row>
     <row r="343">
@@ -15582,13 +15582,13 @@
         <v>0</v>
       </c>
       <c r="I343" t="n">
-        <v>3345243.683620767</v>
+        <v>1581245.415233454</v>
       </c>
       <c r="J343" t="n">
         <v>0</v>
       </c>
       <c r="K343" t="n">
-        <v>7016.188949134201</v>
+        <v>3316.444976056926</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
         <v>0</v>
       </c>
       <c r="N343" t="n">
-        <v>3345243.683620767</v>
+        <v>1581245.415233454</v>
       </c>
     </row>
     <row r="344">
@@ -15626,13 +15626,13 @@
         <v>0</v>
       </c>
       <c r="I344" t="n">
-        <v>3345243.683620767</v>
+        <v>1581245.415233454</v>
       </c>
       <c r="J344" t="n">
-        <v>2342.005102902651</v>
+        <v>1107.02991520497</v>
       </c>
       <c r="K344" t="n">
-        <v>9358.194052036852</v>
+        <v>4423.474891261896</v>
       </c>
       <c r="L344" t="n">
         <v>0</v>
@@ -15641,7 +15641,7 @@
         <v>0</v>
       </c>
       <c r="N344" t="n">
-        <v>3347585.688723669</v>
+        <v>1582352.445148658</v>
       </c>
     </row>
     <row r="345">
@@ -15670,13 +15670,13 @@
         <v>0</v>
       </c>
       <c r="I345" t="n">
-        <v>3347585.688723669</v>
+        <v>1582352.445148658</v>
       </c>
       <c r="J345" t="n">
-        <v>2343.644740675576</v>
+        <v>1107.804946848657</v>
       </c>
       <c r="K345" t="n">
-        <v>11701.83879271243</v>
+        <v>5531.279838110553</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -15685,7 +15685,7 @@
         <v>0</v>
       </c>
       <c r="N345" t="n">
-        <v>3349929.333464345</v>
+        <v>1583460.250095507</v>
       </c>
     </row>
     <row r="346">
@@ -15714,13 +15714,13 @@
         <v>0</v>
       </c>
       <c r="I346" t="n">
-        <v>3349929.333464345</v>
+        <v>1583460.250095507</v>
       </c>
       <c r="J346" t="n">
-        <v>2345.285526358522</v>
+        <v>1108.580521091819</v>
       </c>
       <c r="K346" t="n">
-        <v>14047.12431907095</v>
+        <v>6639.860359202372</v>
       </c>
       <c r="L346" t="n">
         <v>0</v>
@@ -15729,7 +15729,7 @@
         <v>0</v>
       </c>
       <c r="N346" t="n">
-        <v>3352274.618990703</v>
+        <v>1584568.830616599</v>
       </c>
     </row>
     <row r="347">
@@ -15758,13 +15758,13 @@
         <v>0</v>
       </c>
       <c r="I347" t="n">
-        <v>3352274.618990703</v>
+        <v>1584568.830616599</v>
       </c>
       <c r="J347" t="n">
-        <v>2346.927460755222</v>
+        <v>1109.356638314668</v>
       </c>
       <c r="K347" t="n">
-        <v>16394.05177982617</v>
+        <v>7749.21699751704</v>
       </c>
       <c r="L347" t="n">
         <v>0</v>
@@ -15773,7 +15773,7 @@
         <v>0</v>
       </c>
       <c r="N347" t="n">
-        <v>3354621.546451459</v>
+        <v>1585678.187254914</v>
       </c>
     </row>
     <row r="348">
@@ -15802,13 +15802,13 @@
         <v>0</v>
       </c>
       <c r="I348" t="n">
-        <v>3354621.546451459</v>
+        <v>1585678.187254914</v>
       </c>
       <c r="J348" t="n">
         <v>0</v>
       </c>
       <c r="K348" t="n">
-        <v>16394.05177982617</v>
+        <v>7749.21699751704</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -15817,7 +15817,7 @@
         <v>0</v>
       </c>
       <c r="N348" t="n">
-        <v>3354621.546451459</v>
+        <v>1585678.187254914</v>
       </c>
     </row>
     <row r="349">
@@ -15846,13 +15846,13 @@
         <v>0</v>
       </c>
       <c r="I349" t="n">
-        <v>3354621.546451459</v>
+        <v>1585678.187254914</v>
       </c>
       <c r="J349" t="n">
         <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>16394.05177982617</v>
+        <v>7749.21699751704</v>
       </c>
       <c r="L349" t="n">
         <v>0</v>
@@ -15861,7 +15861,7 @@
         <v>0</v>
       </c>
       <c r="N349" t="n">
-        <v>3354621.546451459</v>
+        <v>1585678.187254914</v>
       </c>
     </row>
     <row r="350">
@@ -15890,13 +15890,13 @@
         <v>0</v>
       </c>
       <c r="I350" t="n">
-        <v>3354621.546451459</v>
+        <v>1585678.187254914</v>
       </c>
       <c r="J350" t="n">
-        <v>2348.570544670802</v>
+        <v>1110.133298897184</v>
       </c>
       <c r="K350" t="n">
-        <v>18742.62232449697</v>
+        <v>8859.350296414224</v>
       </c>
       <c r="L350" t="n">
         <v>0</v>
@@ -15905,7 +15905,7 @@
         <v>0</v>
       </c>
       <c r="N350" t="n">
-        <v>3356970.11699613</v>
+        <v>1586788.320553811</v>
       </c>
     </row>
     <row r="351">
@@ -15934,13 +15934,13 @@
         <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>3356970.11699613</v>
+        <v>1586788.320553811</v>
       </c>
       <c r="J351" t="n">
-        <v>2350.214778908994</v>
+        <v>1110.91050321958</v>
       </c>
       <c r="K351" t="n">
-        <v>21092.83710340597</v>
+        <v>9970.260799633805</v>
       </c>
       <c r="L351" t="n">
         <v>0</v>
@@ -15949,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="N351" t="n">
-        <v>3359320.331775039</v>
+        <v>1587899.23105703</v>
       </c>
     </row>
     <row r="352">
@@ -15978,13 +15978,13 @@
         <v>0</v>
       </c>
       <c r="I352" t="n">
-        <v>3359320.331775039</v>
+        <v>1587899.23105703</v>
       </c>
       <c r="J352" t="n">
-        <v>2351.860164275859</v>
+        <v>1111.688251662999</v>
       </c>
       <c r="K352" t="n">
-        <v>23444.69726768183</v>
+        <v>11081.9490512968</v>
       </c>
       <c r="L352" t="n">
         <v>0</v>
@@ -15993,7 +15993,7 @@
         <v>0</v>
       </c>
       <c r="N352" t="n">
-        <v>3361672.191939314</v>
+        <v>1589010.919308693</v>
       </c>
     </row>
     <row r="353">
@@ -16022,13 +16022,13 @@
         <v>0</v>
       </c>
       <c r="I353" t="n">
-        <v>3361672.191939314</v>
+        <v>1589010.919308693</v>
       </c>
       <c r="J353" t="n">
-        <v>2353.506701576523</v>
+        <v>1112.466544607887</v>
       </c>
       <c r="K353" t="n">
-        <v>25798.20396925835</v>
+        <v>12194.41559590469</v>
       </c>
       <c r="L353" t="n">
         <v>0</v>
@@ -16037,7 +16037,7 @@
         <v>0</v>
       </c>
       <c r="N353" t="n">
-        <v>3364025.698640891</v>
+        <v>1590123.385853301</v>
       </c>
     </row>
     <row r="354">
@@ -16066,13 +16066,13 @@
         <v>0</v>
       </c>
       <c r="I354" t="n">
-        <v>3364025.698640891</v>
+        <v>1590123.385853301</v>
       </c>
       <c r="J354" t="n">
-        <v>2355.154391618446</v>
+        <v>1113.245382435853</v>
       </c>
       <c r="K354" t="n">
-        <v>28153.35836087679</v>
+        <v>13307.66097834054</v>
       </c>
       <c r="L354" t="n">
         <v>0</v>
@@ -16081,7 +16081,7 @@
         <v>0</v>
       </c>
       <c r="N354" t="n">
-        <v>3366380.853032509</v>
+        <v>1591236.631235737</v>
       </c>
     </row>
     <row r="355">
@@ -16110,13 +16110,13 @@
         <v>0</v>
       </c>
       <c r="I355" t="n">
-        <v>3366380.853032509</v>
+        <v>1591236.631235737</v>
       </c>
       <c r="J355" t="n">
         <v>0</v>
       </c>
       <c r="K355" t="n">
-        <v>28153.35836087679</v>
+        <v>13307.66097834054</v>
       </c>
       <c r="L355" t="n">
         <v>0</v>
@@ -16125,7 +16125,7 @@
         <v>0</v>
       </c>
       <c r="N355" t="n">
-        <v>3366380.853032509</v>
+        <v>1591236.631235737</v>
       </c>
     </row>
     <row r="356">
@@ -16154,13 +16154,13 @@
         <v>0</v>
       </c>
       <c r="I356" t="n">
-        <v>3366380.853032509</v>
+        <v>1591236.631235737</v>
       </c>
       <c r="J356" t="n">
         <v>0</v>
       </c>
       <c r="K356" t="n">
-        <v>28153.35836087679</v>
+        <v>13307.66097834054</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="N356" t="n">
-        <v>3366380.853032509</v>
+        <v>1591236.631235737</v>
       </c>
     </row>
     <row r="357">
@@ -16198,13 +16198,13 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>3366380.853032509</v>
+        <v>1591236.631235737</v>
       </c>
       <c r="J357" t="n">
-        <v>2356.80323520815</v>
+        <v>1114.02476552804</v>
       </c>
       <c r="K357" t="n">
-        <v>30510.16159608494</v>
+        <v>14421.68574386858</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -16213,7 +16213,7 @@
         <v>0</v>
       </c>
       <c r="N357" t="n">
-        <v>3368737.656267717</v>
+        <v>1592350.656001265</v>
       </c>
     </row>
     <row r="358">
@@ -16242,13 +16242,13 @@
         <v>0</v>
       </c>
       <c r="I358" t="n">
-        <v>3368737.656267717</v>
+        <v>1592350.656001265</v>
       </c>
       <c r="J358" t="n">
-        <v>2358.453233153094</v>
+        <v>1114.804694266524</v>
       </c>
       <c r="K358" t="n">
-        <v>32868.61482923804</v>
+        <v>15536.49043813511</v>
       </c>
       <c r="L358" t="n">
         <v>0</v>
@@ -16257,7 +16257,7 @@
         <v>0</v>
       </c>
       <c r="N358" t="n">
-        <v>3371096.109500871</v>
+        <v>1593465.460695532</v>
       </c>
     </row>
     <row r="359">
@@ -16286,13 +16286,13 @@
         <v>0</v>
       </c>
       <c r="I359" t="n">
-        <v>3371096.109500871</v>
+        <v>1593465.460695532</v>
       </c>
       <c r="J359" t="n">
-        <v>2360.104386261664</v>
+        <v>1115.585169032915</v>
       </c>
       <c r="K359" t="n">
-        <v>35228.7192154997</v>
+        <v>16652.07560716802</v>
       </c>
       <c r="L359" t="n">
         <v>0</v>
@@ -16301,7 +16301,7 @@
         <v>0</v>
       </c>
       <c r="N359" t="n">
-        <v>3373456.213887132</v>
+        <v>1594581.045864565</v>
       </c>
     </row>
     <row r="360">
@@ -16330,13 +16330,13 @@
         <v>0</v>
       </c>
       <c r="I360" t="n">
-        <v>3373456.213887132</v>
+        <v>1594581.045864565</v>
       </c>
       <c r="J360" t="n">
-        <v>2361.75669534225</v>
+        <v>1116.366190209752</v>
       </c>
       <c r="K360" t="n">
-        <v>37590.47591084195</v>
+        <v>17768.44179737777</v>
       </c>
       <c r="L360" t="n">
         <v>0</v>
@@ -16345,7 +16345,7 @@
         <v>0</v>
       </c>
       <c r="N360" t="n">
-        <v>3375817.970582474</v>
+        <v>1595697.412054774</v>
       </c>
     </row>
     <row r="361">
@@ -16374,13 +16374,13 @@
         <v>0</v>
       </c>
       <c r="I361" t="n">
-        <v>3375817.970582474</v>
+        <v>1595697.412054774</v>
       </c>
       <c r="J361" t="n">
-        <v>2363.410161204636</v>
+        <v>1117.147758179577</v>
       </c>
       <c r="K361" t="n">
-        <v>39953.88607204659</v>
+        <v>18885.58955555735</v>
       </c>
       <c r="L361" t="n">
         <v>0</v>
@@ -16389,7 +16389,7 @@
         <v>0</v>
       </c>
       <c r="N361" t="n">
-        <v>3378181.380743679</v>
+        <v>1596814.559812954</v>
       </c>
     </row>
     <row r="362">
@@ -16418,13 +16418,13 @@
         <v>0</v>
       </c>
       <c r="I362" t="n">
-        <v>3378181.380743679</v>
+        <v>1596814.559812954</v>
       </c>
       <c r="J362" t="n">
         <v>0</v>
       </c>
       <c r="K362" t="n">
-        <v>39953.88607204659</v>
+        <v>18885.58955555735</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -16433,7 +16433,7 @@
         <v>0</v>
       </c>
       <c r="N362" t="n">
-        <v>3378181.380743679</v>
+        <v>1596814.559812954</v>
       </c>
     </row>
     <row r="363">
@@ -16462,13 +16462,13 @@
         <v>0</v>
       </c>
       <c r="I363" t="n">
-        <v>3378181.380743679</v>
+        <v>1596814.559812954</v>
       </c>
       <c r="J363" t="n">
         <v>0</v>
       </c>
       <c r="K363" t="n">
-        <v>39953.88607204659</v>
+        <v>18885.58955555735</v>
       </c>
       <c r="L363" t="n">
         <v>0</v>
@@ -16477,7 +16477,7 @@
         <v>0</v>
       </c>
       <c r="N363" t="n">
-        <v>3378181.380743679</v>
+        <v>1596814.559812954</v>
       </c>
     </row>
     <row r="364">
@@ -16506,13 +16506,13 @@
         <v>0</v>
       </c>
       <c r="I364" t="n">
-        <v>3378181.380743679</v>
+        <v>1596814.559812954</v>
       </c>
       <c r="J364" t="n">
-        <v>2365.064784658607</v>
+        <v>1117.929873324931</v>
       </c>
       <c r="K364" t="n">
-        <v>42318.9508567052</v>
+        <v>20003.51942888228</v>
       </c>
       <c r="L364" t="n">
         <v>0</v>
@@ -16521,7 +16521,7 @@
         <v>0</v>
       </c>
       <c r="N364" t="n">
-        <v>3380546.445528338</v>
+        <v>1597932.489686279</v>
       </c>
     </row>
     <row r="365">
@@ -16550,13 +16550,13 @@
         <v>0</v>
       </c>
       <c r="I365" t="n">
-        <v>3380546.445528338</v>
+        <v>1597932.489686279</v>
       </c>
       <c r="J365" t="n">
-        <v>2366.720566514414</v>
+        <v>1118.712536029285</v>
       </c>
       <c r="K365" t="n">
-        <v>44685.67142321961</v>
+        <v>21122.23196491157</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="N365" t="n">
-        <v>3382913.166094852</v>
+        <v>1599051.202222308</v>
       </c>
     </row>
     <row r="366">
@@ -16594,13 +16594,13 @@
         <v>0</v>
       </c>
       <c r="I366" t="n">
-        <v>3382913.166094852</v>
+        <v>1599051.202222308</v>
       </c>
       <c r="J366" t="n">
-        <v>2368.377507582773</v>
+        <v>1119.495746675879</v>
       </c>
       <c r="K366" t="n">
-        <v>47054.04893080238</v>
+        <v>22241.72771158745</v>
       </c>
       <c r="L366" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="N366" t="n">
-        <v>3385281.543602435</v>
+        <v>1600170.697968984</v>
       </c>
     </row>
     <row r="367">
@@ -16638,22 +16638,22 @@
         <v>1</v>
       </c>
       <c r="I367" t="n">
-        <v>3385281.543602435</v>
+        <v>1600170.697968984</v>
       </c>
       <c r="J367" t="n">
-        <v>2370.035608675797</v>
+        <v>1120.279505647952</v>
       </c>
       <c r="K367" t="n">
-        <v>49424.08453947818</v>
+        <v>23362.0072172354</v>
       </c>
       <c r="L367" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="M367" t="n">
-        <v>-34424.08453947818</v>
+        <v>126637.9927827646</v>
       </c>
       <c r="N367" t="n">
-        <v>3372651.579211111</v>
+        <v>1451290.977474632</v>
       </c>
     </row>
     <row r="368">
@@ -16682,13 +16682,13 @@
         <v>0</v>
       </c>
       <c r="I368" t="n">
-        <v>3372651.579211111</v>
+        <v>1451290.977474632</v>
       </c>
       <c r="J368" t="n">
-        <v>2361.193370605819</v>
+        <v>1016.04881333001</v>
       </c>
       <c r="K368" t="n">
-        <v>2361.193370605819</v>
+        <v>1016.04881333001</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -16697,7 +16697,7 @@
         <v>0</v>
       </c>
       <c r="N368" t="n">
-        <v>3375012.772581717</v>
+        <v>1452307.026287962</v>
       </c>
     </row>
     <row r="369">
@@ -16726,13 +16726,13 @@
         <v>0</v>
       </c>
       <c r="I369" t="n">
-        <v>3375012.772581717</v>
+        <v>1452307.026287962</v>
       </c>
       <c r="J369" t="n">
         <v>0</v>
       </c>
       <c r="K369" t="n">
-        <v>2361.193370605819</v>
+        <v>1016.04881333001</v>
       </c>
       <c r="L369" t="n">
         <v>0</v>
@@ -16741,7 +16741,7 @@
         <v>0</v>
       </c>
       <c r="N369" t="n">
-        <v>3375012.772581717</v>
+        <v>1452307.026287962</v>
       </c>
     </row>
     <row r="370">
@@ -16770,13 +16770,13 @@
         <v>0</v>
       </c>
       <c r="I370" t="n">
-        <v>3375012.772581717</v>
+        <v>1452307.026287962</v>
       </c>
       <c r="J370" t="n">
         <v>0</v>
       </c>
       <c r="K370" t="n">
-        <v>2361.193370605819</v>
+        <v>1016.04881333001</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
@@ -16785,7 +16785,7 @@
         <v>0</v>
       </c>
       <c r="N370" t="n">
-        <v>3375012.772581717</v>
+        <v>1452307.026287962</v>
       </c>
     </row>
     <row r="371">
@@ -16814,13 +16814,13 @@
         <v>0</v>
       </c>
       <c r="I371" t="n">
-        <v>3375012.772581717</v>
+        <v>1452307.026287962</v>
       </c>
       <c r="J371" t="n">
-        <v>2362.846442084294</v>
+        <v>1016.760149104288</v>
       </c>
       <c r="K371" t="n">
-        <v>4724.039812690113</v>
+        <v>2032.808962434297</v>
       </c>
       <c r="L371" t="n">
         <v>0</v>
@@ -16829,7 +16829,7 @@
         <v>0</v>
       </c>
       <c r="N371" t="n">
-        <v>3377375.619023801</v>
+        <v>1453323.786437066</v>
       </c>
     </row>
     <row r="372">
@@ -16858,13 +16858,13 @@
         <v>0</v>
       </c>
       <c r="I372" t="n">
-        <v>3377375.619023801</v>
+        <v>1453323.786437066</v>
       </c>
       <c r="J372" t="n">
-        <v>2364.500670878682</v>
+        <v>1017.471982884454</v>
       </c>
       <c r="K372" t="n">
-        <v>7088.540483568795</v>
+        <v>3050.280945318751</v>
       </c>
       <c r="L372" t="n">
         <v>0</v>
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="N372" t="n">
-        <v>3379740.11969468</v>
+        <v>1454341.258419951</v>
       </c>
     </row>
     <row r="373">
@@ -16902,13 +16902,13 @@
         <v>0</v>
       </c>
       <c r="I373" t="n">
-        <v>3379740.11969468</v>
+        <v>1454341.258419951</v>
       </c>
       <c r="J373" t="n">
-        <v>2366.156057798304</v>
+        <v>1018.184315019753</v>
       </c>
       <c r="K373" t="n">
-        <v>9454.696541367099</v>
+        <v>4068.465260338504</v>
       </c>
       <c r="L373" t="n">
         <v>0</v>
@@ -16917,7 +16917,7 @@
         <v>0</v>
       </c>
       <c r="N373" t="n">
-        <v>3382106.275752478</v>
+        <v>1455359.44273497</v>
       </c>
     </row>
     <row r="374">
@@ -16946,13 +16946,13 @@
         <v>0</v>
       </c>
       <c r="I374" t="n">
-        <v>3382106.275752478</v>
+        <v>1455359.44273497</v>
       </c>
       <c r="J374" t="n">
-        <v>2367.81260365434</v>
+        <v>1018.897145858733</v>
       </c>
       <c r="K374" t="n">
-        <v>11822.50914502144</v>
+        <v>5087.362406197237</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -16961,7 +16961,7 @@
         <v>0</v>
       </c>
       <c r="N374" t="n">
-        <v>3384474.088356132</v>
+        <v>1456378.339880829</v>
       </c>
     </row>
     <row r="375">
@@ -16990,13 +16990,13 @@
         <v>0</v>
       </c>
       <c r="I375" t="n">
-        <v>3384474.088356132</v>
+        <v>1456378.339880829</v>
       </c>
       <c r="J375" t="n">
-        <v>2369.470309257973</v>
+        <v>1019.61047575064</v>
       </c>
       <c r="K375" t="n">
-        <v>14191.97945427941</v>
+        <v>6106.972881947877</v>
       </c>
       <c r="L375" t="n">
         <v>0</v>
@@ -17005,7 +17005,7 @@
         <v>0</v>
       </c>
       <c r="N375" t="n">
-        <v>3386843.55866539</v>
+        <v>1457397.95035658</v>
       </c>
     </row>
     <row r="376">
@@ -17034,13 +17034,13 @@
         <v>0</v>
       </c>
       <c r="I376" t="n">
-        <v>3386843.55866539</v>
+        <v>1457397.95035658</v>
       </c>
       <c r="J376" t="n">
         <v>0</v>
       </c>
       <c r="K376" t="n">
-        <v>14191.97945427941</v>
+        <v>6106.972881947877</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -17049,7 +17049,7 @@
         <v>0</v>
       </c>
       <c r="N376" t="n">
-        <v>3386843.55866539</v>
+        <v>1457397.95035658</v>
       </c>
     </row>
   </sheetData>
